--- a/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="548" documentId="11_0354F80925A16C94F44275D1D09B3032E8EAA263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899CD50E-EBA5-4E4C-B757-EFBEAC403F48}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="11_0354F80925A16C94F44275D1D09B3032E8EAA263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83EC4935-CB8A-46BD-BB1F-E3306A6680D9}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,6 +15,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="110">
   <si>
     <t>Project ID</t>
   </si>
@@ -39,142 +42,184 @@
     <t>Title</t>
   </si>
   <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Beneficiary Category</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Donors</t>
+  </si>
+  <si>
+    <t>Gender (% female)</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>SEH Taxonomy</t>
+  </si>
+  <si>
+    <t>RISE Taxonomy</t>
+  </si>
+  <si>
+    <t>Flagship</t>
+  </si>
+  <si>
+    <t>Indirect Category</t>
+  </si>
+  <si>
+    <t>Indirect Taxonomy</t>
+  </si>
+  <si>
+    <t>Addressing food and energy crisis in North Macedonia</t>
+  </si>
+  <si>
+    <t>http://open.undp.org/projects/00144953</t>
+  </si>
+  <si>
+    <t>Accelerating just energy transition</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>Green Finance Facility to Improve Air Quality and Combat Climate Change in North Macedonia</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00144270</t>
+  </si>
+  <si>
+    <t>Expected annual energy saved</t>
+  </si>
+  <si>
+    <t>81,000 MWh tonnes</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>GHG Emissions Reduction</t>
+  </si>
+  <si>
+    <t>Estimated GHG emissions avoided (tCO2e/year)</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Renewable capacity added</t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex disaggregated) of sub-loans (RE/EE) extended by PFIs </t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Total value of sub-loans extended</t>
+  </si>
+  <si>
+    <t>$30.39 M</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Total value of performance- based payments allocated:</t>
+  </si>
+  <si>
+    <t>USD 3.039 M</t>
+  </si>
+  <si>
+    <t>Capacity Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
+  </si>
+  <si>
+    <t>Number of loan officers trained on gender-disaggregated data collection and analysis</t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of individuals reached through marketing efforts  </t>
+  </si>
+  <si>
+    <t>Expected annual energy saved  (MWh)</t>
+  </si>
+  <si>
+    <t>5,200 MWh</t>
+  </si>
+  <si>
+    <t>Estimated GHG emissions avoided tCO2e/year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total value of loans extended: </t>
+  </si>
+  <si>
+    <t>USD 6.5 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of loans extended by banks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
+  </si>
+  <si>
+    <t>Tackling Air Pollution in Skopje</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00110061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculation of emissions </t>
+  </si>
+  <si>
+    <t>5.56t in 2019</t>
+  </si>
+  <si>
     <t>Output Title</t>
   </si>
   <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>Budget</t>
-  </si>
-  <si>
-    <t>Beneficiary Category</t>
-  </si>
-  <si>
-    <t>Indicator</t>
-  </si>
-  <si>
-    <t>Baseline</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Donors</t>
-  </si>
-  <si>
-    <t>Gender (% female)</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
     <t>Comments</t>
   </si>
   <si>
-    <t>Tag</t>
-  </si>
-  <si>
-    <t>SEH Taxonomy</t>
-  </si>
-  <si>
-    <t>RISE Taxonomy</t>
-  </si>
-  <si>
-    <t>Flagship</t>
-  </si>
-  <si>
-    <t>Indirect Category</t>
-  </si>
-  <si>
-    <t>Indirect Taxonomy</t>
-  </si>
-  <si>
-    <t>Addressing food and energy crisis in North Macedonia</t>
-  </si>
-  <si>
-    <t>http://open.undp.org/projects/00144953</t>
-  </si>
-  <si>
-    <t>Accelerating just energy transition</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
-    <t>Green Finance Facility to Improve Air Quality and Combat Climate Change in North Macedonia</t>
+    <t>USD 44.4 M</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
   </si>
   <si>
     <t>Output 1: SMEs have greater access to finance for accelerating a transition to renewable energy and energy efficiency solutions. No. in Quantum: 00132098</t>
   </si>
   <si>
-    <t>https://open.undp.org/projects/00144270</t>
-  </si>
-  <si>
     <t>Other Energy Services</t>
-  </si>
-  <si>
-    <t>Expected annual energy saved</t>
-  </si>
-  <si>
-    <t>81,000 MWh tonnes</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
-  </si>
-  <si>
-    <t>Renewable Energy</t>
-  </si>
-  <si>
-    <t>GHG Emissions Reduction</t>
-  </si>
-  <si>
-    <t>Estimated GHG emissions avoided (tCO2e/year)</t>
-  </si>
-  <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
-    <t>Renewable capacity added</t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex disaggregated) of sub-loans (RE/EE) extended by PFIs </t>
-  </si>
-  <si>
-    <t>Total value of sub-loans extended</t>
-  </si>
-  <si>
-    <t>$30.39 M</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>Total value of performance- based payments allocated:</t>
-  </si>
-  <si>
-    <t>USD 3.039 M</t>
-  </si>
-  <si>
-    <t>Capacity Training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
-  </si>
-  <si>
-    <t>Number of loan officers trained on gender-disaggregated data collection and analysis</t>
-  </si>
-  <si>
-    <t>Campaign Participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of individuals reached through marketing efforts  </t>
   </si>
   <si>
     <t>"Output 2: Target groups/ households, especially women and female headed households have greater access to finance for accelerating a transition to RE and EE solutions. No. in Quantum: 00132099
@@ -184,46 +229,10 @@
     <t xml:space="preserve">Expected annual energy saved </t>
   </si>
   <si>
-    <t>5,200 MWh</t>
-  </si>
-  <si>
-    <t>Estimated GHG emissions avoided tCO2e/year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total value of loans extended: </t>
-  </si>
-  <si>
-    <t>USD 6.5 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of loans extended by banks </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
-  </si>
-  <si>
-    <t>Tackling Air Pollution in Skopje</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00110061</t>
+    <t>USD 2.15 mil</t>
   </si>
   <si>
     <t>Low emission district concept demonstrated (Decrease of polluting emissions from the selected area)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculation of emissions </t>
-  </si>
-  <si>
-    <t>5.56t in 2019</t>
-  </si>
-  <si>
-    <t>USD 44.4 M</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>USD 2.15 mil</t>
   </si>
   <si>
     <t>CO2 Emissions Reduction</t>
@@ -481,7 +490,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -590,43 +599,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -635,7 +607,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -727,36 +699,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -766,9 +708,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -794,15 +733,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -815,24 +748,42 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1139,49 +1090,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1B1400-35FF-426D-9AE6-BEF15E5709CF}">
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="32.7109375" customWidth="1"/>
-    <col min="14" max="14" width="46" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="45" t="s">
+    <row r="1" spans="1:19">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="H1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="I1" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="30" t="s">
@@ -1190,13 +1140,13 @@
       <c r="L1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="36" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="30" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="30" t="s">
@@ -1208,777 +1158,689 @@
       <c r="R1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="36"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="36">
+        <v>144953</v>
+      </c>
+      <c r="B2" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="C2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="46"/>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="46">
-        <v>144953</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="38">
+        <v>95000</v>
+      </c>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="48">
-        <v>95000</v>
-      </c>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46" t="s">
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+    </row>
+    <row r="3" spans="1:19" ht="64.5" customHeight="1">
+      <c r="A3" s="36">
+        <v>144270</v>
+      </c>
+      <c r="B3" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="46" t="s">
+      <c r="C3" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-    </row>
-    <row r="3" spans="1:21" ht="64.5" customHeight="1">
-      <c r="A3" s="46">
-        <v>144270</v>
-      </c>
-      <c r="B3" s="46" t="s">
+      <c r="D3" s="38">
+        <v>44400000</v>
+      </c>
+      <c r="E3" s="38"/>
+      <c r="F3" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="G3" s="42">
+        <v>0</v>
+      </c>
+      <c r="H3" s="43"/>
+      <c r="I3" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="48">
-        <v>44400000</v>
-      </c>
-      <c r="F3" s="48" t="s">
+      <c r="O3" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="P3" s="36"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="36"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="38"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="53">
-        <v>0</v>
-      </c>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55" t="s">
+      <c r="F4" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46" t="s">
+      <c r="G4" s="42">
+        <v>0</v>
+      </c>
+      <c r="H4" s="45">
+        <v>75654</v>
+      </c>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="36"/>
+    </row>
+    <row r="5" spans="1:19" ht="15" customHeight="1">
+      <c r="A5" s="38"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="F5" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="46"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="46"/>
-    </row>
-    <row r="4" spans="1:21" ht="15" customHeight="1">
-      <c r="A4" s="48"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="48" t="s">
+      <c r="G5" s="42">
+        <v>0</v>
+      </c>
+      <c r="H5" s="47">
+        <v>8.1</v>
+      </c>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="36"/>
+    </row>
+    <row r="6" spans="1:19" ht="40.5" customHeight="1">
+      <c r="A6" s="38"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="F6" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="53">
-        <v>0</v>
-      </c>
-      <c r="I4" s="56">
-        <v>75654</v>
-      </c>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" s="46"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="30"/>
-      <c r="U4" s="46"/>
-    </row>
-    <row r="5" spans="1:21" ht="15" customHeight="1">
-      <c r="A5" s="48"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="48" t="s">
+      <c r="G6" s="42">
+        <v>0</v>
+      </c>
+      <c r="H6" s="47">
+        <v>105</v>
+      </c>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="36"/>
+    </row>
+    <row r="7" spans="1:19" ht="24.75" customHeight="1">
+      <c r="A7" s="38"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="F7" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="53">
-        <v>0</v>
-      </c>
-      <c r="I5" s="58">
-        <v>8.1</v>
-      </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="46"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="46"/>
-      <c r="P5" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" s="46"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="46"/>
-    </row>
-    <row r="6" spans="1:21" ht="40.5" customHeight="1">
-      <c r="A6" s="48"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="48" t="s">
+      <c r="G7" s="42">
+        <v>0</v>
+      </c>
+      <c r="H7" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="53">
-        <v>0</v>
-      </c>
-      <c r="I6" s="58">
-        <v>105</v>
-      </c>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="46"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="46"/>
-    </row>
-    <row r="7" spans="1:21" ht="24.75" customHeight="1">
-      <c r="A7" s="48"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="52" t="s">
+      <c r="N7" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="S7" s="36"/>
+    </row>
+    <row r="8" spans="1:19" ht="27.75" customHeight="1">
+      <c r="A8" s="38"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="53">
-        <v>0</v>
-      </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="55" t="s">
+      <c r="G8" s="42">
+        <v>0</v>
+      </c>
+      <c r="H8" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="46" t="s">
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="36"/>
+    </row>
+    <row r="9" spans="1:19" ht="55.5" customHeight="1">
+      <c r="A9" s="38"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q7" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R7" s="46"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="30"/>
-      <c r="U7" s="46"/>
-    </row>
-    <row r="8" spans="1:21" ht="27.75" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="52" t="s">
+      <c r="F9" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="53">
-        <v>0</v>
-      </c>
-      <c r="I8" s="60"/>
-      <c r="J8" s="55" t="s">
+      <c r="G9" s="42">
+        <v>0</v>
+      </c>
+      <c r="H9" s="48">
+        <v>20</v>
+      </c>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="36"/>
+    </row>
+    <row r="10" spans="1:19" ht="41.25" customHeight="1">
+      <c r="A10" s="38"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q8" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R8" s="46"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="46"/>
-    </row>
-    <row r="9" spans="1:21" ht="55.5" customHeight="1">
-      <c r="A9" s="48"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="48" t="s">
+      <c r="G10" s="42">
+        <v>0</v>
+      </c>
+      <c r="H10" s="48">
+        <v>20</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="36"/>
+    </row>
+    <row r="11" spans="1:19" ht="39.75" customHeight="1">
+      <c r="A11" s="38"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="F11" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="53">
-        <v>0</v>
-      </c>
-      <c r="I9" s="59">
-        <v>20</v>
-      </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R9" s="46"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="46"/>
-    </row>
-    <row r="10" spans="1:21" ht="41.25" customHeight="1">
-      <c r="A10" s="48"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="48" t="s">
+      <c r="G11" s="42">
+        <v>0</v>
+      </c>
+      <c r="H11" s="48">
+        <v>7000</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="36"/>
+    </row>
+    <row r="12" spans="1:19" ht="27.75" customHeight="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="42">
+        <v>0</v>
+      </c>
+      <c r="H12" s="48">
+        <v>5200</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="36"/>
+    </row>
+    <row r="13" spans="1:19" ht="24.75" customHeight="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="42">
+        <v>0</v>
+      </c>
+      <c r="H13" s="50">
+        <v>4856.8</v>
+      </c>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="36"/>
+    </row>
+    <row r="14" spans="1:19" ht="20.25" customHeight="1">
+      <c r="A14" s="38"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="42">
+        <v>0</v>
+      </c>
+      <c r="H14" s="48">
+        <v>2.6</v>
+      </c>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="36"/>
+    </row>
+    <row r="15" spans="1:19" ht="20.25" customHeight="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="51" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="42">
+        <v>0</v>
+      </c>
+      <c r="H15" s="48"/>
+      <c r="I15" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="36"/>
+    </row>
+    <row r="16" spans="1:19" ht="27">
+      <c r="A16" s="38"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="42">
+        <v>0</v>
+      </c>
+      <c r="H16" s="48">
+        <v>650</v>
+      </c>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="36"/>
+    </row>
+    <row r="17" spans="1:19" ht="27">
+      <c r="A17" s="38"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="42">
+        <v>0</v>
+      </c>
+      <c r="H17" s="48">
+        <v>20</v>
+      </c>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="36"/>
+    </row>
+    <row r="18" spans="1:19" ht="27">
+      <c r="A18" s="38"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="42">
+        <v>0</v>
+      </c>
+      <c r="H18" s="48">
+        <v>20</v>
+      </c>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="36"/>
+    </row>
+    <row r="19" spans="1:19" ht="27">
+      <c r="A19" s="38"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="53">
-        <v>0</v>
-      </c>
-      <c r="I10" s="59">
-        <v>20</v>
-      </c>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="46"/>
-      <c r="P10" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" s="46"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="46"/>
-    </row>
-    <row r="11" spans="1:21" ht="39.75" customHeight="1">
-      <c r="A11" s="48"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="53">
-        <v>0</v>
-      </c>
-      <c r="I11" s="59">
-        <v>7000</v>
-      </c>
-      <c r="J11" s="46"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="61"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="46"/>
-      <c r="P11" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R11" s="46"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="46"/>
-    </row>
-    <row r="12" spans="1:21" ht="27.75" customHeight="1">
-      <c r="A12" s="48"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="62" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="53">
-        <v>0</v>
-      </c>
-      <c r="I12" s="59"/>
-      <c r="J12" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="K12" s="46"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q12" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R12" s="46"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="46"/>
-    </row>
-    <row r="13" spans="1:21" ht="24.75" customHeight="1">
-      <c r="A13" s="48"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="53">
-        <v>0</v>
-      </c>
-      <c r="I13" s="63">
-        <v>4856.8</v>
-      </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R13" s="46"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="46"/>
-    </row>
-    <row r="14" spans="1:21" ht="20.25" customHeight="1">
-      <c r="A14" s="48"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="53">
-        <v>0</v>
-      </c>
-      <c r="I14" s="59">
-        <v>2.6</v>
-      </c>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="46"/>
-      <c r="P14" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="R14" s="46"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="46"/>
-    </row>
-    <row r="15" spans="1:21" ht="20.25" customHeight="1">
-      <c r="A15" s="48"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="64" t="s">
+      <c r="F19" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="42">
+        <v>0</v>
+      </c>
+      <c r="H19" s="53">
+        <v>1000</v>
+      </c>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="36"/>
+    </row>
+    <row r="20" spans="1:19" ht="45.75">
+      <c r="A20" s="52">
+        <v>110061</v>
+      </c>
+      <c r="B20" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="H15" s="53">
-        <v>0</v>
-      </c>
-      <c r="I15" s="59"/>
-      <c r="J15" s="55" t="s">
+      <c r="C20" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q15" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R15" s="46"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="46"/>
-    </row>
-    <row r="16" spans="1:21" ht="27">
-      <c r="A16" s="48"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="64" t="s">
+      <c r="D20" s="52">
+        <v>2150000</v>
+      </c>
+      <c r="E20" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="53">
-        <v>0</v>
-      </c>
-      <c r="I16" s="59">
-        <v>650</v>
-      </c>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q16" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" s="46"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="46"/>
-    </row>
-    <row r="17" spans="1:21" ht="27">
-      <c r="A17" s="48"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="64" t="s">
+      <c r="G20" s="52"/>
+      <c r="H20" s="52">
+        <v>2.23</v>
+      </c>
+      <c r="I20" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="53">
-        <v>0</v>
-      </c>
-      <c r="I17" s="59">
-        <v>20</v>
-      </c>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q17" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R17" s="46"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="46"/>
-    </row>
-    <row r="18" spans="1:21" ht="27">
-      <c r="A18" s="48"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="53">
-        <v>0</v>
-      </c>
-      <c r="I18" s="59">
-        <v>20</v>
-      </c>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q18" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R18" s="46"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="46"/>
-    </row>
-    <row r="19" spans="1:21" ht="27">
-      <c r="A19" s="48"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="64" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="53">
-        <v>0</v>
-      </c>
-      <c r="I19" s="66">
-        <v>1000</v>
-      </c>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="46"/>
-      <c r="P19" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="46"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="46"/>
-    </row>
-    <row r="20" spans="1:21" ht="45.75">
-      <c r="A20" s="65">
-        <v>110061</v>
-      </c>
-      <c r="B20" s="65" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="67" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="65">
-        <v>2150000</v>
-      </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="65"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R20" s="46"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="46"/>
-    </row>
-    <row r="21" spans="1:21" ht="30.75">
-      <c r="A21" s="65">
-        <v>109164</v>
-      </c>
-      <c r="B21" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="65">
-        <v>5.56</v>
-      </c>
-      <c r="I21" s="65">
-        <v>3.33</v>
-      </c>
-      <c r="J21" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="46"/>
-      <c r="P21" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q21" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="R21" s="46"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="46"/>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="G22" s="8"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="36"/>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="F21" s="8"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="F22" s="8"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
       <c r="P22" s="29"/>
       <c r="Q22" s="29"/>
       <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="G23" s="8"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="G24" s="8"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="F23" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C12:C19"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="C3:C11"/>
-  </mergeCells>
   <dataValidations count="6">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4 F13" xr:uid="{C35AD5E7-9C05-4A11-9F71-36719D32C290}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T23" xr:uid="{1E190A99-9BFF-4CE9-AC67-306E550850B7}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4 E13" xr:uid="{C35AD5E7-9C05-4A11-9F71-36719D32C290}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R22" xr:uid="{1E190A99-9BFF-4CE9-AC67-306E550850B7}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S23" xr:uid="{2001F045-7211-4118-BD15-E46516BB0DAB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q22" xr:uid="{2001F045-7211-4118-BD15-E46516BB0DAB}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R23" xr:uid="{96AE7F23-217A-4AD9-B279-78255CC36D9A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P22" xr:uid="{96AE7F23-217A-4AD9-B279-78255CC36D9A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q23" xr:uid="{7679577C-5057-4CAE-A580-533A5173DCDC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O22" xr:uid="{7679577C-5057-4CAE-A580-533A5173DCDC}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P23" xr:uid="{8BF837C9-DADF-4F73-B2BD-0382CD04DE67}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N22" xr:uid="{8BF837C9-DADF-4F73-B2BD-0382CD04DE67}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{E526A5E1-C5A6-4AA2-ABA5-1BC765442B72}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{A8C7CD7F-F779-4D37-8E5B-FC1B6B146550}"/>
-    <hyperlink ref="D20" r:id="rId3" xr:uid="{1057C5CB-3ACE-49CD-81D9-B6566CBF4DA9}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{E526A5E1-C5A6-4AA2-ABA5-1BC765442B72}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{A8C7CD7F-F779-4D37-8E5B-FC1B6B146550}"/>
+    <hyperlink ref="C20" r:id="rId3" xr:uid="{1057C5CB-3ACE-49CD-81D9-B6566CBF4DA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1988,7 +1850,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F12 F14 F16:F19 F2:F3</xm:sqref>
+          <xm:sqref>E2:E3 E14 E16:E19 E5:E6 E9:E12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2020,55 +1882,55 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="L1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="Q1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="S1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="T1" s="29" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="29" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -2076,10 +1938,10 @@
         <v>144953</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2" s="8">
         <v>95000</v>
@@ -2091,10 +1953,10 @@
       <c r="J2" s="3"/>
       <c r="N2" s="33"/>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2102,21 +1964,21 @@
         <v>144270</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F3" s="8"/>
       <c r="N3" s="33"/>
       <c r="P3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S3" s="29"/>
       <c r="T3" s="29"/>
@@ -2124,30 +1986,30 @@
     <row r="4" spans="1:20" ht="39.75" customHeight="1">
       <c r="A4" s="8"/>
       <c r="B4" s="34"/>
-      <c r="C4" s="36" t="s">
-        <v>25</v>
+      <c r="C4" s="58" t="s">
+        <v>60</v>
       </c>
       <c r="D4" s="34"/>
       <c r="E4" s="34"/>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H4" s="11">
         <v>0</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="31" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N4" s="33"/>
       <c r="P4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S4" s="29"/>
       <c r="T4" s="29"/>
@@ -2155,14 +2017,14 @@
     <row r="5" spans="1:20" ht="15" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="34"/>
-      <c r="C5" s="36"/>
+      <c r="C5" s="58"/>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
       <c r="F5" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H5" s="11">
         <v>0</v>
@@ -2172,10 +2034,10 @@
       </c>
       <c r="N5" s="33"/>
       <c r="P5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S5" s="29"/>
       <c r="T5" s="29"/>
@@ -2183,14 +2045,14 @@
     <row r="6" spans="1:20" ht="15" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="34"/>
-      <c r="C6" s="36"/>
+      <c r="C6" s="58"/>
       <c r="D6" s="34"/>
       <c r="E6" s="34"/>
       <c r="F6" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H6" s="11">
         <v>0</v>
@@ -2200,10 +2062,10 @@
       </c>
       <c r="N6" s="33"/>
       <c r="P6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S6" s="29"/>
       <c r="T6" s="29"/>
@@ -2211,14 +2073,14 @@
     <row r="7" spans="1:20" ht="40.5" customHeight="1">
       <c r="A7" s="8"/>
       <c r="B7" s="34"/>
-      <c r="C7" s="36"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H7" s="11">
         <v>0</v>
@@ -2228,10 +2090,10 @@
       </c>
       <c r="N7" s="33"/>
       <c r="P7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S7" s="29"/>
       <c r="T7" s="29"/>
@@ -2239,28 +2101,28 @@
     <row r="8" spans="1:20" ht="24.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="34"/>
-      <c r="C8" s="36"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="34"/>
       <c r="E8" s="34"/>
       <c r="F8" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H8" s="11">
         <v>0</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="N8" s="33"/>
       <c r="P8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S8" s="29"/>
       <c r="T8" s="29"/>
@@ -2268,28 +2130,28 @@
     <row r="9" spans="1:20" ht="27.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="36"/>
+      <c r="C9" s="58"/>
       <c r="D9" s="34"/>
       <c r="E9" s="34"/>
       <c r="F9" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H9" s="11">
         <v>0</v>
       </c>
       <c r="I9" s="16"/>
       <c r="J9" s="31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N9" s="33"/>
       <c r="P9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S9" s="29"/>
       <c r="T9" s="29"/>
@@ -2297,14 +2159,14 @@
     <row r="10" spans="1:20" ht="55.5" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="34"/>
-      <c r="C10" s="36"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="34"/>
       <c r="E10" s="34"/>
       <c r="F10" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H10" s="11">
         <v>0</v>
@@ -2314,10 +2176,10 @@
       </c>
       <c r="N10" s="33"/>
       <c r="P10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S10" s="29"/>
       <c r="T10" s="29"/>
@@ -2325,14 +2187,14 @@
     <row r="11" spans="1:20" ht="41.25" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="34"/>
-      <c r="C11" s="36"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="34"/>
       <c r="E11" s="34"/>
       <c r="F11" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H11" s="11">
         <v>0</v>
@@ -2342,10 +2204,10 @@
       </c>
       <c r="N11" s="33"/>
       <c r="P11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="29"/>
@@ -2353,14 +2215,14 @@
     <row r="12" spans="1:20" ht="39.75" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="34"/>
-      <c r="C12" s="36"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
       <c r="F12" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H12" s="11">
         <v>0</v>
@@ -2371,10 +2233,10 @@
       <c r="L12" s="7"/>
       <c r="N12" s="33"/>
       <c r="P12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S12" s="29"/>
       <c r="T12" s="29"/>
@@ -2382,28 +2244,28 @@
     <row r="13" spans="1:20" ht="27.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="34"/>
-      <c r="C13" s="36" t="s">
-        <v>48</v>
+      <c r="C13" s="58" t="s">
+        <v>62</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
       <c r="F13" s="8"/>
       <c r="G13" s="9" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H13" s="11">
         <v>0</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N13" s="33"/>
       <c r="P13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S13" s="29"/>
       <c r="T13" s="29"/>
@@ -2411,14 +2273,14 @@
     <row r="14" spans="1:20" ht="24.75" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="34"/>
-      <c r="C14" s="36"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H14" s="11">
         <v>0</v>
@@ -2428,10 +2290,10 @@
       </c>
       <c r="N14" s="33"/>
       <c r="P14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S14" s="29"/>
       <c r="T14" s="29"/>
@@ -2439,14 +2301,14 @@
     <row r="15" spans="1:20" ht="20.25" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="34"/>
-      <c r="C15" s="36"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
       <c r="F15" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H15" s="11">
         <v>0</v>
@@ -2456,10 +2318,10 @@
       </c>
       <c r="N15" s="33"/>
       <c r="P15" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Q15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="S15" s="29"/>
       <c r="T15" s="29"/>
@@ -2467,26 +2329,26 @@
     <row r="16" spans="1:20" ht="20.25" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="34"/>
-      <c r="C16" s="36"/>
+      <c r="C16" s="58"/>
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
       <c r="F16" s="18"/>
       <c r="G16" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H16" s="11">
         <v>0</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="31" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N16" s="33"/>
       <c r="P16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S16" s="29"/>
       <c r="T16" s="29"/>
@@ -2494,14 +2356,14 @@
     <row r="17" spans="1:20" ht="27">
       <c r="A17" s="8"/>
       <c r="B17" s="34"/>
-      <c r="C17" s="36"/>
+      <c r="C17" s="58"/>
       <c r="D17" s="34"/>
       <c r="E17" s="34"/>
       <c r="F17" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H17" s="11">
         <v>0</v>
@@ -2511,10 +2373,10 @@
       </c>
       <c r="N17" s="33"/>
       <c r="P17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S17" s="29"/>
       <c r="T17" s="29"/>
@@ -2522,14 +2384,14 @@
     <row r="18" spans="1:20" ht="27">
       <c r="A18" s="8"/>
       <c r="B18" s="34"/>
-      <c r="C18" s="36"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34"/>
       <c r="E18" s="34"/>
       <c r="F18" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H18" s="11">
         <v>0</v>
@@ -2539,10 +2401,10 @@
       </c>
       <c r="N18" s="33"/>
       <c r="P18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S18" s="29"/>
       <c r="T18" s="29"/>
@@ -2550,14 +2412,14 @@
     <row r="19" spans="1:20" ht="27">
       <c r="A19" s="8"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="36"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
       <c r="F19" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H19" s="11">
         <v>0</v>
@@ -2567,10 +2429,10 @@
       </c>
       <c r="N19" s="33"/>
       <c r="P19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S19" s="29"/>
       <c r="T19" s="29"/>
@@ -2578,14 +2440,14 @@
     <row r="20" spans="1:20" ht="27">
       <c r="A20" s="8"/>
       <c r="B20" s="34"/>
-      <c r="C20" s="37"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
       <c r="F20" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H20" s="11">
         <v>0</v>
@@ -2596,10 +2458,10 @@
       <c r="J20" s="17"/>
       <c r="N20" s="33"/>
       <c r="P20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S20" s="29"/>
       <c r="T20" s="29"/>
@@ -2609,14 +2471,14 @@
         <v>110061</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="22"/>
@@ -2625,10 +2487,10 @@
       <c r="J21" s="18"/>
       <c r="N21" s="33"/>
       <c r="P21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S21" s="29"/>
       <c r="T21" s="29"/>
@@ -2637,20 +2499,20 @@
       <c r="A22" s="24">
         <v>109164</v>
       </c>
-      <c r="B22" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
+      <c r="B22" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
       <c r="F22" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G22" s="26" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I22" s="27">
         <v>3.33</v>
@@ -2658,10 +2520,10 @@
       <c r="J22" s="18"/>
       <c r="N22" s="33"/>
       <c r="P22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S22" s="29"/>
       <c r="T22" s="29"/>
@@ -2753,28 +2615,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="29" t="s">
         <v>9</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2782,10 +2644,10 @@
         <v>144953</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="8">
         <v>95000</v>
@@ -2801,86 +2663,86 @@
         <v>144270</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="39.75" customHeight="1">
+      <c r="A4" s="61">
+        <v>144270</v>
+      </c>
+      <c r="B4" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="G4" s="11">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30.75">
+      <c r="A5" s="61"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="39.75" customHeight="1">
-      <c r="A4" s="39">
-        <v>144270</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="11">
-        <v>0</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30.75">
-      <c r="A5" s="39"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G5" s="11">
         <v>0</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="39"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
       <c r="E6" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G6" s="11">
         <v>0</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="40.5" customHeight="1">
-      <c r="A7" s="39"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
       <c r="E7" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G7" s="11">
         <v>0</v>
@@ -2890,182 +2752,182 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A8" s="39"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
       <c r="E8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="9" t="s">
+    </row>
+    <row r="9" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A9" s="61"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="15" t="s">
+      <c r="G9" s="11">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="39"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="9" t="s">
+    <row r="10" spans="1:11" ht="55.5" customHeight="1">
+      <c r="A10" s="61"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="16" t="s">
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A11" s="61"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="55.5" customHeight="1">
-      <c r="A10" s="39"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="8" t="s">
+      <c r="G11" s="11">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="39.75" customHeight="1">
+      <c r="A12" s="61"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="41.25" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="11">
-        <v>0</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="39.75" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A13" s="61">
+        <v>144270</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0</v>
+      </c>
+      <c r="H13" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="11">
-        <v>0</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="39">
-        <v>144270</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="9" t="s">
+    </row>
+    <row r="14" spans="1:11" ht="24.75" customHeight="1">
+      <c r="A14" s="61"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="20.25" customHeight="1">
+      <c r="A15" s="61"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="20.25" customHeight="1">
+      <c r="A16" s="61"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="15" t="s">
+    </row>
+    <row r="17" spans="1:9" ht="27">
+      <c r="A17" s="61"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A14" s="39"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="11">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="11">
-        <v>0</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="11">
-        <v>0</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="27">
-      <c r="A17" s="39"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="G17" s="11">
         <v>0</v>
@@ -3075,51 +2937,51 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="27">
-      <c r="A18" s="39"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
       <c r="E18" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="27">
+      <c r="A19" s="61"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="27">
+      <c r="A20" s="61"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="11">
-        <v>0</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="27">
-      <c r="A19" s="39"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="11">
-        <v>0</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="27">
-      <c r="A20" s="39"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="F20" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G20" s="11">
         <v>0</v>
@@ -3134,13 +2996,13 @@
         <v>110061</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E21" s="20"/>
       <c r="F21" s="22"/>
@@ -3152,22 +3014,22 @@
       <c r="A22" s="24">
         <v>109164</v>
       </c>
-      <c r="B22" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+      <c r="B22" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
       <c r="E22" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I22" s="18"/>
     </row>
@@ -3219,160 +3081,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="41" t="s">
-        <v>78</v>
+      <c r="A2" s="63" t="s">
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="41"/>
+      <c r="A3" s="63"/>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="41"/>
+      <c r="A4" s="63"/>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="42" t="s">
-        <v>84</v>
+      <c r="A5" s="64" t="s">
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="42"/>
+      <c r="A6" s="64"/>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="42"/>
+      <c r="A7" s="64"/>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="42"/>
+      <c r="A8" s="64"/>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="42"/>
+      <c r="A9" s="64"/>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="43" t="s">
-        <v>94</v>
+      <c r="A10" s="65" t="s">
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="43"/>
+      <c r="A11" s="65"/>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="44" t="s">
-        <v>98</v>
+      <c r="A12" s="66" t="s">
+        <v>100</v>
       </c>
       <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="66"/>
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="66"/>
+      <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="44"/>
-      <c r="B13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="44"/>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3387,6 +3249,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
@@ -3397,7 +3268,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3646,23 +3517,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1F45FA-ADB1-42D5-8002-7349D9DEF3AA}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0849318C-6090-4401-8D9F-FDDD7A2B862B}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027502D3-96EC-47DD-8A36-DB96D446584B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1F45FA-ADB1-42D5-8002-7349D9DEF3AA}"/>
 </file>
--- a/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="620" documentId="11_0354F80925A16C94F44275D1D09B3032E8EAA263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72E80B7E-98DF-4200-99F3-9F33A262DC55}"/>
+  <xr:revisionPtr revIDLastSave="633" documentId="11_0354F80925A16C94F44275D1D09B3032E8EAA263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4569D06-E7BC-4CDC-8665-F00E65A0E19D}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="125">
   <si>
     <t>Project ID</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Technology</t>
+  </si>
+  <si>
+    <t>Market Intervention</t>
   </si>
   <si>
     <t>Policy or Regulatory Framework</t>
@@ -127,133 +130,133 @@
     <t>National</t>
   </si>
   <si>
+    <t>Green Finance Facility to Improve Air Quality and Combat Climate Change in North Macedonia</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00144270</t>
+  </si>
+  <si>
+    <t>Energy Efficiency Services</t>
+  </si>
+  <si>
+    <t>Expected annual energy saved (MJ)</t>
+  </si>
+  <si>
+    <t>81,000 MWh tonnes</t>
+  </si>
+  <si>
+    <t>GHG Emissions Reduction</t>
+  </si>
+  <si>
+    <t>Estimated GHG emissions avoided (tCO2e/year)</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Renewable capacity added</t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex disaggregated) of sub-loans (RE/EE) extended by PFIs </t>
+  </si>
+  <si>
+    <t>Total value of sub-loans extended</t>
+  </si>
+  <si>
+    <t>Business Model</t>
+  </si>
+  <si>
+    <t>Total value of performance- based payments allocated:</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
+  </si>
+  <si>
+    <t>Number of loan officers trained on gender-disaggregated data collection and analysis</t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of individuals reached through marketing efforts  </t>
+  </si>
+  <si>
+    <t>Expected annual energy saved  (MJ)</t>
+  </si>
+  <si>
+    <t>5,200 MWh -&gt; convert to MJ 18720000</t>
+  </si>
+  <si>
+    <t>Estimated GHG emissions avoided tCO2e/year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total value of loans extended: </t>
+  </si>
+  <si>
+    <t>USD 6.5 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of loans extended by banks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
+  </si>
+  <si>
+    <t>Tackling Air Pollution in Skopje</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00110061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculation of emissions </t>
+  </si>
+  <si>
+    <t>5.56t in 2019</t>
+  </si>
+  <si>
+    <t>Output Title</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
     <t>Energy Efficiency</t>
   </si>
   <si>
-    <t>Green Finance Facility to Improve Air Quality and Combat Climate Change in North Macedonia</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00144270</t>
-  </si>
-  <si>
-    <t>Energy Efficiency Services</t>
-  </si>
-  <si>
-    <t>Expected annual energy saved (MJ)</t>
-  </si>
-  <si>
-    <t>81,000 MWh tonnes</t>
+    <t>USD 44.4 M</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Output 1: SMEs have greater access to finance for accelerating a transition to renewable energy and energy efficiency solutions. No. in Quantum: 00132098</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <t>Expected annual energy saved</t>
   </si>
   <si>
     <t>Close the gap on energy access</t>
   </si>
   <si>
-    <t>GHG Emissions Reduction</t>
-  </si>
-  <si>
-    <t>Estimated GHG emissions avoided (tCO2e/year)</t>
-  </si>
-  <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
-    <t>Renewable capacity added</t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex disaggregated) of sub-loans (RE/EE) extended by PFIs </t>
-  </si>
-  <si>
-    <t>Market Intervention</t>
-  </si>
-  <si>
-    <t>Total value of sub-loans extended</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>Total value of performance- based payments allocated:</t>
+    <t>$30.39 M</t>
+  </si>
+  <si>
+    <t>USD 3.039 M</t>
   </si>
   <si>
     <t>Capacity Training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
-  </si>
-  <si>
-    <t>Number of loan officers trained on gender-disaggregated data collection and analysis</t>
-  </si>
-  <si>
-    <t>Campaign Participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of individuals reached through marketing efforts  </t>
-  </si>
-  <si>
-    <t>Expected annual energy saved  (MJ)</t>
-  </si>
-  <si>
-    <t>5,200 MWh -&gt; convert to MJ 18720000</t>
-  </si>
-  <si>
-    <t>Estimated GHG emissions avoided tCO2e/year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total value of loans extended: </t>
-  </si>
-  <si>
-    <t>USD 6.5 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of loans extended by banks </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
-  </si>
-  <si>
-    <t>Tackling Air Pollution in Skopje</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00110061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculation of emissions </t>
-  </si>
-  <si>
-    <t>5.56t in 2019</t>
-  </si>
-  <si>
-    <t>Output Title</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>USD 44.4 M</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>Output 1: SMEs have greater access to finance for accelerating a transition to renewable energy and energy efficiency solutions. No. in Quantum: 00132098</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
-  </si>
-  <si>
-    <t>Expected annual energy saved</t>
-  </si>
-  <si>
-    <t>$30.39 M</t>
-  </si>
-  <si>
-    <t>USD 3.039 M</t>
   </si>
   <si>
     <t>"Output 2: Target groups/ households, especially women and female headed households have greater access to finance for accelerating a transition to RE and EE solutions. No. in Quantum: 00132099
@@ -385,9 +388,6 @@
   </si>
   <si>
     <t>Support for the development of small enterprises in the energy transition market</t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
   </si>
   <si>
     <t>Number of people who benefits from training for enterprises on the energy business and energy finance. </t>
@@ -1181,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1B1400-35FF-426D-9AE6-BEF15E5709CF}">
-  <dimension ref="A1:Z23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1198,11 +1198,13 @@
     <col min="15" max="15" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:22">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -1263,28 +1265,31 @@
       <c r="T1" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="59" t="s">
+      <c r="U1" s="58" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" ht="106.5">
+      <c r="V1" s="59" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="106.5">
       <c r="A2" s="33">
         <v>144953</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="37">
         <v>95000</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
@@ -1292,37 +1297,30 @@
       <c r="J2" s="33"/>
       <c r="K2" s="33"/>
       <c r="L2" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" s="39"/>
       <c r="N2" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2" s="39"/>
       <c r="Q2" s="39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R2" s="39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S2" s="37"/>
-      <c r="T2" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="U2" s="37"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="33" t="s">
+      <c r="T2" s="39"/>
+      <c r="U2" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="33"/>
-    </row>
-    <row r="3" spans="1:26" ht="64.5" customHeight="1">
+      <c r="V2" s="37"/>
+    </row>
+    <row r="3" spans="1:22" ht="64.5" customHeight="1">
       <c r="A3" s="33">
         <v>144270</v>
       </c>
@@ -1353,11 +1351,11 @@
       <c r="J3" s="33"/>
       <c r="K3" s="33"/>
       <c r="L3" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="39"/>
       <c r="N3" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" s="39"/>
       <c r="P3" s="39"/>
@@ -1365,26 +1363,19 @@
       <c r="R3" s="39"/>
       <c r="S3" s="37"/>
       <c r="T3" s="39"/>
-      <c r="U3" s="37"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y3" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z3" s="33"/>
-    </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1">
+      <c r="U3" s="39"/>
+      <c r="V3" s="37"/>
+    </row>
+    <row r="4" spans="1:22" ht="15" customHeight="1">
       <c r="A4" s="37"/>
       <c r="B4" s="42"/>
       <c r="C4" s="42"/>
       <c r="D4" s="42"/>
       <c r="E4" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>37</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>38</v>
       </c>
       <c r="G4" s="39">
         <v>0</v>
@@ -1396,11 +1387,11 @@
       <c r="J4" s="33"/>
       <c r="K4" s="33"/>
       <c r="L4" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M4" s="39"/>
       <c r="N4" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" s="39"/>
       <c r="P4" s="39"/>
@@ -1408,26 +1399,19 @@
       <c r="R4" s="39"/>
       <c r="S4" s="37"/>
       <c r="T4" s="39"/>
-      <c r="U4" s="37"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y4" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z4" s="33"/>
-    </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1">
+      <c r="U4" s="39"/>
+      <c r="V4" s="37"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" customHeight="1">
       <c r="A5" s="37"/>
       <c r="B5" s="42"/>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="44" t="s">
         <v>39</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>40</v>
       </c>
       <c r="G5" s="39">
         <v>0</v>
@@ -1439,11 +1423,11 @@
       <c r="J5" s="33"/>
       <c r="K5" s="33"/>
       <c r="L5" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" s="39"/>
       <c r="N5" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" s="39"/>
       <c r="P5" s="39"/>
@@ -1451,26 +1435,19 @@
       <c r="R5" s="39"/>
       <c r="S5" s="37"/>
       <c r="T5" s="39"/>
-      <c r="U5" s="37"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y5" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z5" s="33"/>
-    </row>
-    <row r="6" spans="1:26" ht="40.5" customHeight="1">
+      <c r="U5" s="39"/>
+      <c r="V5" s="37"/>
+    </row>
+    <row r="6" spans="1:22" ht="40.5" customHeight="1">
       <c r="A6" s="37"/>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
       <c r="E6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="44" t="s">
         <v>41</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>42</v>
       </c>
       <c r="G6" s="39">
         <v>0</v>
@@ -1482,11 +1459,11 @@
       <c r="J6" s="33"/>
       <c r="K6" s="33"/>
       <c r="L6" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6" s="39"/>
       <c r="N6" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" s="39"/>
       <c r="P6" s="39"/>
@@ -1494,26 +1471,19 @@
       <c r="R6" s="39"/>
       <c r="S6" s="37"/>
       <c r="T6" s="39"/>
-      <c r="U6" s="37"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y6" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z6" s="33"/>
-    </row>
-    <row r="7" spans="1:26" ht="24.75" customHeight="1">
+      <c r="U6" s="39"/>
+      <c r="V6" s="37"/>
+    </row>
+    <row r="7" spans="1:22" ht="24.75" customHeight="1">
       <c r="A7" s="37"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
       <c r="E7" s="42" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G7" s="39">
         <v>0</v>
@@ -1524,40 +1494,33 @@
       <c r="J7" s="33"/>
       <c r="K7" s="33"/>
       <c r="L7" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" s="39"/>
       <c r="N7" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" s="39"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="37"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="37"/>
-      <c r="W7" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z7" s="33"/>
-    </row>
-    <row r="8" spans="1:26" ht="27.75" customHeight="1">
+      <c r="T7" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="U7" s="39"/>
+      <c r="V7" s="37"/>
+    </row>
+    <row r="8" spans="1:22" ht="27.75" customHeight="1">
       <c r="A8" s="37"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
       <c r="E8" s="42" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G8" s="39">
         <v>0</v>
@@ -1568,38 +1531,33 @@
       <c r="J8" s="33"/>
       <c r="K8" s="33"/>
       <c r="L8" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="39"/>
       <c r="N8" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" s="39"/>
       <c r="P8" s="39"/>
       <c r="Q8" s="39"/>
       <c r="R8" s="39"/>
       <c r="S8" s="37"/>
-      <c r="T8" s="39"/>
-      <c r="U8" s="37"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y8" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z8" s="33"/>
-    </row>
-    <row r="9" spans="1:26" ht="55.5" customHeight="1">
+      <c r="T8" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="U8" s="39"/>
+      <c r="V8" s="37"/>
+    </row>
+    <row r="9" spans="1:22" ht="55.5" customHeight="1">
       <c r="A9" s="37"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
       <c r="E9" s="37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G9" s="39">
         <v>0</v>
@@ -1611,11 +1569,11 @@
       <c r="J9" s="33"/>
       <c r="K9" s="33"/>
       <c r="L9" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M9" s="39"/>
       <c r="N9" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O9" s="39"/>
       <c r="P9" s="39"/>
@@ -1623,26 +1581,19 @@
       <c r="R9" s="39"/>
       <c r="S9" s="37"/>
       <c r="T9" s="39"/>
-      <c r="U9" s="37"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y9" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z9" s="33"/>
-    </row>
-    <row r="10" spans="1:26" ht="41.25" customHeight="1">
+      <c r="U9" s="39"/>
+      <c r="V9" s="37"/>
+    </row>
+    <row r="10" spans="1:22" ht="41.25" customHeight="1">
       <c r="A10" s="37"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
       <c r="E10" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="38" t="s">
         <v>47</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>49</v>
       </c>
       <c r="G10" s="39">
         <v>0</v>
@@ -1654,11 +1605,11 @@
       <c r="J10" s="33"/>
       <c r="K10" s="33"/>
       <c r="L10" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M10" s="39"/>
       <c r="N10" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O10" s="39"/>
       <c r="P10" s="39"/>
@@ -1666,26 +1617,19 @@
       <c r="R10" s="39"/>
       <c r="S10" s="37"/>
       <c r="T10" s="39"/>
-      <c r="U10" s="37"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y10" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z10" s="33"/>
-    </row>
-    <row r="11" spans="1:26" ht="39.75" customHeight="1">
+      <c r="U10" s="39"/>
+      <c r="V10" s="37"/>
+    </row>
+    <row r="11" spans="1:22" ht="39.75" customHeight="1">
       <c r="A11" s="37"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
       <c r="E11" s="37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G11" s="39">
         <v>0</v>
@@ -1697,11 +1641,11 @@
       <c r="J11" s="33"/>
       <c r="K11" s="47"/>
       <c r="L11" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M11" s="39"/>
       <c r="N11" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O11" s="39"/>
       <c r="P11" s="39"/>
@@ -1709,17 +1653,10 @@
       <c r="R11" s="39"/>
       <c r="S11" s="37"/>
       <c r="T11" s="39"/>
-      <c r="U11" s="37"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y11" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z11" s="33"/>
-    </row>
-    <row r="12" spans="1:26" ht="27.75" customHeight="1">
+      <c r="U11" s="39"/>
+      <c r="V11" s="37"/>
+    </row>
+    <row r="12" spans="1:22" ht="27.75" customHeight="1">
       <c r="A12" s="37"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
@@ -1728,7 +1665,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G12" s="39">
         <v>0</v>
@@ -1737,16 +1674,16 @@
         <v>18720000</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J12" s="33"/>
       <c r="K12" s="33"/>
       <c r="L12" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M12" s="39"/>
       <c r="N12" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O12" s="39"/>
       <c r="P12" s="39"/>
@@ -1754,26 +1691,19 @@
       <c r="R12" s="39"/>
       <c r="S12" s="37"/>
       <c r="T12" s="39"/>
-      <c r="U12" s="37"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y12" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z12" s="33"/>
-    </row>
-    <row r="13" spans="1:26" ht="24.75" customHeight="1">
+      <c r="U12" s="39"/>
+      <c r="V12" s="37"/>
+    </row>
+    <row r="13" spans="1:22" ht="24.75" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
       <c r="E13" s="37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G13" s="39">
         <v>0</v>
@@ -1785,11 +1715,11 @@
       <c r="J13" s="33"/>
       <c r="K13" s="33"/>
       <c r="L13" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M13" s="39"/>
       <c r="N13" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O13" s="39"/>
       <c r="P13" s="39"/>
@@ -1797,26 +1727,19 @@
       <c r="R13" s="39"/>
       <c r="S13" s="37"/>
       <c r="T13" s="39"/>
-      <c r="U13" s="37"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y13" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z13" s="33"/>
-    </row>
-    <row r="14" spans="1:26" ht="20.25" customHeight="1">
+      <c r="U13" s="39"/>
+      <c r="V13" s="37"/>
+    </row>
+    <row r="14" spans="1:22" ht="20.25" customHeight="1">
       <c r="A14" s="37"/>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
       <c r="D14" s="42"/>
       <c r="E14" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="49" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>40</v>
       </c>
       <c r="G14" s="39">
         <v>0</v>
@@ -1828,11 +1751,11 @@
       <c r="J14" s="33"/>
       <c r="K14" s="33"/>
       <c r="L14" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M14" s="39"/>
       <c r="N14" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O14" s="39"/>
       <c r="P14" s="39"/>
@@ -1840,26 +1763,19 @@
       <c r="R14" s="39"/>
       <c r="S14" s="37"/>
       <c r="T14" s="39"/>
-      <c r="U14" s="37"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y14" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z14" s="33"/>
-    </row>
-    <row r="15" spans="1:26" ht="20.25" customHeight="1">
+      <c r="U14" s="39"/>
+      <c r="V14" s="37"/>
+    </row>
+    <row r="15" spans="1:22" ht="20.25" customHeight="1">
       <c r="A15" s="37"/>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
       <c r="D15" s="42"/>
       <c r="E15" s="50" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G15" s="39">
         <v>0</v>
@@ -1868,43 +1784,38 @@
         <v>6500000</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J15" s="33"/>
       <c r="K15" s="33"/>
       <c r="L15" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M15" s="39"/>
       <c r="N15" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" s="39"/>
       <c r="P15" s="39"/>
       <c r="Q15" s="39"/>
       <c r="R15" s="39"/>
       <c r="S15" s="37"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="37"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y15" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z15" s="33"/>
-    </row>
-    <row r="16" spans="1:26" ht="45.75">
+      <c r="T15" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="U15" s="39"/>
+      <c r="V15" s="37"/>
+    </row>
+    <row r="16" spans="1:22" ht="45.75">
       <c r="A16" s="37"/>
       <c r="B16" s="42"/>
       <c r="C16" s="42"/>
       <c r="D16" s="42"/>
       <c r="E16" s="37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" s="39">
         <v>0</v>
@@ -1916,11 +1827,11 @@
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O16" s="39"/>
       <c r="P16" s="39"/>
@@ -1928,26 +1839,19 @@
       <c r="R16" s="39"/>
       <c r="S16" s="37"/>
       <c r="T16" s="39"/>
-      <c r="U16" s="37"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y16" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z16" s="33"/>
-    </row>
-    <row r="17" spans="1:26" ht="45.75">
+      <c r="U16" s="39"/>
+      <c r="V16" s="37"/>
+    </row>
+    <row r="17" spans="1:22" ht="45.75">
       <c r="A17" s="37"/>
       <c r="B17" s="42"/>
       <c r="C17" s="42"/>
       <c r="D17" s="42"/>
       <c r="E17" s="37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G17" s="39">
         <v>0</v>
@@ -1959,11 +1863,11 @@
       <c r="J17" s="33"/>
       <c r="K17" s="33"/>
       <c r="L17" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O17" s="39"/>
       <c r="P17" s="39"/>
@@ -1971,26 +1875,19 @@
       <c r="R17" s="39"/>
       <c r="S17" s="37"/>
       <c r="T17" s="39"/>
-      <c r="U17" s="37"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y17" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z17" s="33"/>
-    </row>
-    <row r="18" spans="1:26" ht="45.75">
+      <c r="U17" s="39"/>
+      <c r="V17" s="37"/>
+    </row>
+    <row r="18" spans="1:22" ht="45.75">
       <c r="A18" s="37"/>
       <c r="B18" s="42"/>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
       <c r="E18" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="49" t="s">
         <v>47</v>
-      </c>
-      <c r="F18" s="49" t="s">
-        <v>49</v>
       </c>
       <c r="G18" s="39">
         <v>0</v>
@@ -2002,11 +1899,11 @@
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
       <c r="L18" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M18" s="39"/>
       <c r="N18" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O18" s="39"/>
       <c r="P18" s="39"/>
@@ -2014,26 +1911,19 @@
       <c r="R18" s="39"/>
       <c r="S18" s="37"/>
       <c r="T18" s="39"/>
-      <c r="U18" s="37"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y18" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z18" s="33"/>
-    </row>
-    <row r="19" spans="1:26" ht="45.75">
+      <c r="U18" s="39"/>
+      <c r="V18" s="37"/>
+    </row>
+    <row r="19" spans="1:22" ht="45.75">
       <c r="A19" s="37"/>
       <c r="B19" s="42"/>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
       <c r="E19" s="37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G19" s="39">
         <v>0</v>
@@ -2045,11 +1935,11 @@
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
       <c r="L19" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M19" s="39"/>
       <c r="N19" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O19" s="39"/>
       <c r="P19" s="39"/>
@@ -2057,50 +1947,43 @@
       <c r="R19" s="39"/>
       <c r="S19" s="37"/>
       <c r="T19" s="39"/>
-      <c r="U19" s="37"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y19" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z19" s="33"/>
-    </row>
-    <row r="20" spans="1:26" ht="45.75">
+      <c r="U19" s="39"/>
+      <c r="V19" s="37"/>
+    </row>
+    <row r="20" spans="1:22" ht="45.75">
       <c r="A20" s="50">
         <v>110061</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D20" s="50">
         <v>2150000</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G20" s="50"/>
       <c r="H20" s="50">
         <v>2.23</v>
       </c>
       <c r="I20" s="53" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
       <c r="L20" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M20" s="39"/>
       <c r="N20" s="61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O20" s="39"/>
       <c r="P20" s="39"/>
@@ -2108,17 +1991,10 @@
       <c r="R20" s="39"/>
       <c r="S20" s="37"/>
       <c r="T20" s="39"/>
-      <c r="U20" s="37"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y20" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z20" s="33"/>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="U20" s="39"/>
+      <c r="V20" s="37"/>
+    </row>
+    <row r="21" spans="1:22">
       <c r="F21" s="6"/>
       <c r="N21" s="27"/>
       <c r="O21" s="27"/>
@@ -2127,7 +2003,7 @@
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:22">
       <c r="F22" s="6"/>
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
@@ -2136,11 +2012,11 @@
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:22">
       <c r="F23" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S21:S22" xr:uid="{1E190A99-9BFF-4CE9-AC67-306E550850B7}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
     </dataValidation>
@@ -2150,10 +2026,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P20 Q21:Q22" xr:uid="{96AE7F23-217A-4AD9-B279-78255CC36D9A}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O21:P22 Y2:Z20" xr:uid="{7679577C-5057-4CAE-A580-533A5173DCDC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O21:P22" xr:uid="{7679577C-5057-4CAE-A580-533A5173DCDC}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X20 N2:N22" xr:uid="{8BF837C9-DADF-4F73-B2BD-0382CD04DE67}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N22" xr:uid="{8BF837C9-DADF-4F73-B2BD-0382CD04DE67}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O20" xr:uid="{7AFDFACD-238C-4995-A371-0CB44E452D0E}">
@@ -2162,7 +2038,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M20" xr:uid="{46DAB895-E9B1-4522-ABAF-25AE5B633D3B}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T20" xr:uid="{178070A3-1F94-4269-9451-493F2770BB30}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U20" xr:uid="{178070A3-1F94-4269-9451-493F2770BB30}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L20" xr:uid="{4945BA84-8427-4530-86EA-3DBC336EB5D0}">
@@ -2173,6 +2049,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S20" xr:uid="{2832DC64-DEAC-4976-A1E2-F5A781EE6B22}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T20" xr:uid="{9FB228AE-3228-45AB-864A-0D934BACE7A9}">
+      <formula1>"Incentives and Support, Derisking Financial Model, Business Model"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -2220,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -2250,10 +2129,10 @@
         <v>10</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P1" s="27" t="s">
         <v>13</v>
@@ -2276,10 +2155,10 @@
         <v>144953</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="6">
         <v>95000</v>
@@ -2291,10 +2170,10 @@
       <c r="J2" s="3"/>
       <c r="N2" s="31"/>
       <c r="P2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2308,15 +2187,15 @@
         <v>32</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" s="6"/>
       <c r="N3" s="31"/>
       <c r="P3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q3" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S3" s="27"/>
       <c r="T3" s="27"/>
@@ -2325,15 +2204,15 @@
       <c r="A4" s="6"/>
       <c r="B4" s="32"/>
       <c r="C4" s="63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="H4" s="9">
         <v>0</v>
@@ -2344,10 +2223,10 @@
       </c>
       <c r="N4" s="31"/>
       <c r="P4" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Q4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S4" s="27"/>
       <c r="T4" s="27"/>
@@ -2359,10 +2238,10 @@
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
       <c r="F5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -2372,10 +2251,10 @@
       </c>
       <c r="N5" s="31"/>
       <c r="P5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S5" s="27"/>
       <c r="T5" s="27"/>
@@ -2387,10 +2266,10 @@
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -2400,10 +2279,10 @@
       </c>
       <c r="N6" s="31"/>
       <c r="P6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S6" s="27"/>
       <c r="T6" s="27"/>
@@ -2415,10 +2294,10 @@
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -2428,10 +2307,10 @@
       </c>
       <c r="N7" s="31"/>
       <c r="P7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S7" s="27"/>
       <c r="T7" s="27"/>
@@ -2443,10 +2322,10 @@
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2457,10 +2336,10 @@
       </c>
       <c r="N8" s="31"/>
       <c r="P8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q8" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S8" s="27"/>
       <c r="T8" s="27"/>
@@ -2472,10 +2351,10 @@
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -2486,10 +2365,10 @@
       </c>
       <c r="N9" s="31"/>
       <c r="P9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q9" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S9" s="27"/>
       <c r="T9" s="27"/>
@@ -2501,10 +2380,10 @@
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
       <c r="F10" s="6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -2514,10 +2393,10 @@
       </c>
       <c r="N10" s="31"/>
       <c r="P10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S10" s="27"/>
       <c r="T10" s="27"/>
@@ -2529,10 +2408,10 @@
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
       <c r="F11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -2542,10 +2421,10 @@
       </c>
       <c r="N11" s="31"/>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S11" s="27"/>
       <c r="T11" s="27"/>
@@ -2557,10 +2436,10 @@
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
       <c r="F12" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -2571,10 +2450,10 @@
       <c r="L12" s="5"/>
       <c r="N12" s="31"/>
       <c r="P12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S12" s="27"/>
       <c r="T12" s="27"/>
@@ -2583,27 +2462,27 @@
       <c r="A13" s="6"/>
       <c r="B13" s="32"/>
       <c r="C13" s="63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
       <c r="F13" s="6"/>
       <c r="G13" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N13" s="31"/>
       <c r="P13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q13" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S13" s="27"/>
       <c r="T13" s="27"/>
@@ -2615,10 +2494,10 @@
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
       <c r="F14" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -2628,10 +2507,10 @@
       </c>
       <c r="N14" s="31"/>
       <c r="P14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S14" s="27"/>
       <c r="T14" s="27"/>
@@ -2643,10 +2522,10 @@
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
       <c r="F15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -2656,10 +2535,10 @@
       </c>
       <c r="N15" s="31"/>
       <c r="P15" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="Q15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S15" s="27"/>
       <c r="T15" s="27"/>
@@ -2672,21 +2551,21 @@
       <c r="E16" s="32"/>
       <c r="F16" s="16"/>
       <c r="G16" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N16" s="31"/>
       <c r="P16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q16" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S16" s="27"/>
       <c r="T16" s="27"/>
@@ -2698,10 +2577,10 @@
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
       <c r="F17" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2711,10 +2590,10 @@
       </c>
       <c r="N17" s="31"/>
       <c r="P17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S17" s="27"/>
       <c r="T17" s="27"/>
@@ -2726,10 +2605,10 @@
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
       <c r="F18" s="6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2739,10 +2618,10 @@
       </c>
       <c r="N18" s="31"/>
       <c r="P18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S18" s="27"/>
       <c r="T18" s="27"/>
@@ -2754,10 +2633,10 @@
       <c r="D19" s="32"/>
       <c r="E19" s="32"/>
       <c r="F19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2767,10 +2646,10 @@
       </c>
       <c r="N19" s="31"/>
       <c r="P19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S19" s="27"/>
       <c r="T19" s="27"/>
@@ -2782,10 +2661,10 @@
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
       <c r="F20" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2796,10 +2675,10 @@
       <c r="J20" s="15"/>
       <c r="N20" s="31"/>
       <c r="P20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q20" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S20" s="27"/>
       <c r="T20" s="27"/>
@@ -2809,14 +2688,14 @@
         <v>110061</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="20"/>
@@ -2825,10 +2704,10 @@
       <c r="J21" s="16"/>
       <c r="N21" s="31"/>
       <c r="P21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S21" s="27"/>
       <c r="T21" s="27"/>
@@ -2838,19 +2717,19 @@
         <v>109164</v>
       </c>
       <c r="B22" s="62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="62"/>
       <c r="E22" s="62"/>
       <c r="F22" s="23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I22" s="25">
         <v>3.33</v>
@@ -2858,10 +2737,10 @@
       <c r="J22" s="16"/>
       <c r="N22" s="31"/>
       <c r="P22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="S22" s="27"/>
       <c r="T22" s="27"/>
@@ -2982,10 +2861,10 @@
         <v>144953</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="6">
         <v>95000</v>
@@ -3007,10 +2886,10 @@
         <v>32</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="39.75" customHeight="1">
@@ -3018,15 +2897,15 @@
         <v>144270</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="65"/>
       <c r="D4" s="65"/>
       <c r="E4" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4" s="9">
         <v>0</v>
@@ -3041,16 +2920,16 @@
       <c r="C5" s="65"/>
       <c r="D5" s="65"/>
       <c r="E5" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3059,16 +2938,16 @@
       <c r="C6" s="65"/>
       <c r="D6" s="65"/>
       <c r="E6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="G6" s="9">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="40.5" customHeight="1">
@@ -3077,10 +2956,10 @@
       <c r="C7" s="65"/>
       <c r="D7" s="65"/>
       <c r="E7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
@@ -3095,10 +2974,10 @@
       <c r="C8" s="65"/>
       <c r="D8" s="65"/>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="9">
         <v>0</v>
@@ -3113,10 +2992,10 @@
       <c r="C9" s="65"/>
       <c r="D9" s="65"/>
       <c r="E9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G9" s="9">
         <v>0</v>
@@ -3131,16 +3010,16 @@
       <c r="C10" s="65"/>
       <c r="D10" s="65"/>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G10" s="9">
         <v>0</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="41.25" customHeight="1">
@@ -3149,16 +3028,16 @@
       <c r="C11" s="65"/>
       <c r="D11" s="65"/>
       <c r="E11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>49</v>
-      </c>
       <c r="G11" s="9">
         <v>0</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="39.75" customHeight="1">
@@ -3167,16 +3046,16 @@
       <c r="C12" s="65"/>
       <c r="D12" s="65"/>
       <c r="E12" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="9">
         <v>0</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K12" s="5"/>
     </row>
@@ -3185,21 +3064,21 @@
         <v>144270</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="65"/>
       <c r="E13" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G13" s="9">
         <v>0</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="24.75" customHeight="1">
@@ -3208,16 +3087,16 @@
       <c r="C14" s="65"/>
       <c r="D14" s="65"/>
       <c r="E14" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" s="9">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.25" customHeight="1">
@@ -3226,16 +3105,16 @@
       <c r="C15" s="65"/>
       <c r="D15" s="65"/>
       <c r="E15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="G15" s="9">
         <v>0</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
@@ -3244,16 +3123,16 @@
       <c r="C16" s="65"/>
       <c r="D16" s="65"/>
       <c r="E16" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27">
@@ -3262,10 +3141,10 @@
       <c r="C17" s="65"/>
       <c r="D17" s="65"/>
       <c r="E17" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -3280,16 +3159,16 @@
       <c r="C18" s="65"/>
       <c r="D18" s="65"/>
       <c r="E18" s="6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G18" s="9">
         <v>0</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27">
@@ -3298,16 +3177,16 @@
       <c r="C19" s="65"/>
       <c r="D19" s="65"/>
       <c r="E19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>49</v>
-      </c>
       <c r="G19" s="9">
         <v>0</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27">
@@ -3316,10 +3195,10 @@
       <c r="C20" s="65"/>
       <c r="D20" s="65"/>
       <c r="E20" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G20" s="9">
         <v>0</v>
@@ -3334,13 +3213,13 @@
         <v>110061</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="20"/>
@@ -3353,21 +3232,21 @@
         <v>109164</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" s="67"/>
       <c r="D22" s="67"/>
       <c r="E22" s="23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" s="16"/>
     </row>
@@ -3427,74 +3306,74 @@
     </row>
     <row r="2" spans="1:2" ht="45.75">
       <c r="A2" s="68" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
       <c r="A6" s="68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
       <c r="A7" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
       <c r="A8" s="68" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
       <c r="A9" s="68" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
@@ -3502,52 +3381,52 @@
         <v>33</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
       <c r="A12" s="68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B12" s="55" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
       <c r="A13" s="68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" s="69" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="68" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="69" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
       <c r="A15" s="68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
       <c r="A16" s="68" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B16" s="69" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
       <c r="A17" s="68" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="B17" s="55" t="s">
         <v>117</v>
@@ -3563,7 +3442,7 @@
     </row>
     <row r="19" spans="1:2" ht="76.5">
       <c r="A19" s="68" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B19" s="69" t="s">
         <v>120</v>
@@ -3571,7 +3450,7 @@
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" s="68" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="69" t="s">
         <v>121</v>
@@ -3579,7 +3458,7 @@
     </row>
     <row r="21" spans="1:2" ht="45.75">
       <c r="A21" s="68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="70" t="s">
         <v>122</v>
@@ -3608,8 +3487,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3634,6 +3513,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3713,6 +3593,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3872,7 +3757,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{027502D3-96EC-47DD-8A36-DB96D446584B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61DB48B0-5F5D-4664-9BF2-2988CF8E9CA6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="633" documentId="11_0354F80925A16C94F44275D1D09B3032E8EAA263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4569D06-E7BC-4CDC-8665-F00E65A0E19D}"/>
+  <xr:revisionPtr revIDLastSave="848" documentId="11_0354F80925A16C94F44275D1D09B3032E8EAA263" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AC16853-E3EA-4E27-BACC-F0C7AFDF8249}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
+    <sheet name="Projects (2.5)" sheetId="5" state="hidden" r:id="rId1"/>
+    <sheet name="Projects (3)" sheetId="4" r:id="rId2"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId4"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,8 +34,218 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={79EEC1AE-897B-4A90-805B-F768C8A6C2CD}</author>
+    <author>tc={621A9DFD-CCA8-4D76-B5B6-158D5A833901}</author>
+    <author>tc={A08E9D70-5A23-46E7-B9E5-91D2EF7C552F}</author>
+    <author>tc={D2FE1F41-7211-4981-AD33-0A9F681DCFBD}</author>
+    <author>tc={891F3133-B0A9-4747-959A-2C56653BE395}</author>
+    <author>tc={BC0B41C5-54B6-4044-85AB-618F19862654}</author>
+    <author>tc={23B597A5-1B66-4CAB-AA0F-F278334B7E92}</author>
+    <author>tc={66639FD2-4E2E-4171-92B2-2E309852434A}</author>
+    <author>tc={2EBE4A3C-45A5-419E-9453-DCAF8C235A44}</author>
+    <author>tc={C03134EB-0D27-4781-BC31-6E10FCBCA97A}</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{79EEC1AE-897B-4A90-805B-F768C8A6C2CD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I added the donor named based on the web link for this column, please check if this is correct</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="1" shapeId="0" xr:uid="{621A9DFD-CCA8-4D76-B5B6-158D5A833901}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Note to system: The number relates to energy saved not number of beneficiaries
+Reply:
+    Correct.</t>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="2" shapeId="0" xr:uid="{A08E9D70-5A23-46E7-B9E5-91D2EF7C552F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</t>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="3" shapeId="0" xr:uid="{D2FE1F41-7211-4981-AD33-0A9F681DCFBD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tentative/target number of SME beneficiaries of support (tech assistance, "green" loans and performance-based incentives) for RE/EE investments.</t>
+      </text>
+    </comment>
+    <comment ref="I16" authorId="4" shapeId="0" xr:uid="{891F3133-B0A9-4747-959A-2C56653BE395}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This should indicate the number of beneficiaries supported by this intervention
+Reply:
+    It indicates an expected/target number of households/individuals supported (with tech assistance, "green" loans, and ex-post, performance-based incentives) for RE/EE investments.</t>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="5" shapeId="0" xr:uid="{BC0B41C5-54B6-4044-85AB-618F19862654}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This should indicate the volume of investment (US dollars). Thank you for checking if this is correct.
+Reply:
+    This indicates the volume of *ex-post, performance-based incentives* attached to the investments (upon verification). The incentives for these groups of beneficiaries, though are payable by IOM (implementing partner in the project/GFF).</t>
+      </text>
+    </comment>
+    <comment ref="J23" authorId="6" shapeId="0" xr:uid="{23B597A5-1B66-4CAB-AA0F-F278334B7E92}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</t>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="7" shapeId="0" xr:uid="{66639FD2-4E2E-4171-92B2-2E309852434A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Budget taken from web link, please check if this is correct</t>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="8" shapeId="0" xr:uid="{2EBE4A3C-45A5-419E-9453-DCAF8C235A44}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Budget taken from web link, please check if this is correct</t>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="9" shapeId="0" xr:uid="{C03134EB-0D27-4781-BC31-6E10FCBCA97A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Budget taken from web link, please check if this is correct</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={9234F38C-6247-4C32-9C39-0813DCF2450F}</author>
+    <author>tc={7A94FBEE-AD1F-467F-AD57-574F1E79D6C3}</author>
+    <author>tc={CA08CDE2-D4D6-4671-B38F-80F1DB89074F}</author>
+    <author>tc={BDC16EA3-A8E2-496C-BBA7-C59FBD41AC51}</author>
+    <author>tc={952459A9-C6C8-4831-8252-7617B7339F3E}</author>
+    <author>tc={C38306C6-5115-4A98-B84A-C3BE8B9B0A8B}</author>
+    <author>tc={10739C89-E707-417F-AB4E-5ABD4B510B80}</author>
+    <author>tc={8F310A7D-2DE2-4A4C-A359-FA3AEC7579AD}</author>
+    <author>tc={8E2C567E-C0F8-4DD4-B60D-DE770583DE9B}</author>
+    <author>tc={2B238BD5-0FE1-4ABD-837C-4C765A136BD6}</author>
+  </authors>
+  <commentList>
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{9234F38C-6247-4C32-9C39-0813DCF2450F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I added the donor named based on the web link for this column, please check if this is correct</t>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="1" shapeId="0" xr:uid="{7A94FBEE-AD1F-467F-AD57-574F1E79D6C3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Note to system: The number relates to energy saved not number of beneficiaries
+Reply:
+    Correct.</t>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="2" shapeId="0" xr:uid="{CA08CDE2-D4D6-4671-B38F-80F1DB89074F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</t>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="3" shapeId="0" xr:uid="{BDC16EA3-A8E2-496C-BBA7-C59FBD41AC51}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tentative/target number of SME beneficiaries of support (tech assistance, "green" loans and performance-based incentives) for RE/EE investments.</t>
+      </text>
+    </comment>
+    <comment ref="I16" authorId="4" shapeId="0" xr:uid="{952459A9-C6C8-4831-8252-7617B7339F3E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This should indicate the number of beneficiaries supported by this intervention
+Reply:
+    It indicates an expected/target number of households/individuals supported (with tech assistance, "green" loans, and ex-post, performance-based incentives) for RE/EE investments.</t>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="5" shapeId="0" xr:uid="{C38306C6-5115-4A98-B84A-C3BE8B9B0A8B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This should indicate the volume of investment (US dollars). Thank you for checking if this is correct.
+Reply:
+    This indicates the volume of *ex-post, performance-based incentives* attached to the investments (upon verification). The incentives for these groups of beneficiaries, though are payable by IOM (implementing partner in the project/GFF).</t>
+      </text>
+    </comment>
+    <comment ref="J23" authorId="6" shapeId="0" xr:uid="{10739C89-E707-417F-AB4E-5ABD4B510B80}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</t>
+      </text>
+    </comment>
+    <comment ref="D25" authorId="7" shapeId="0" xr:uid="{8F310A7D-2DE2-4A4C-A359-FA3AEC7579AD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Budget taken from web link, please check if this is correct</t>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="8" shapeId="0" xr:uid="{8E2C567E-C0F8-4DD4-B60D-DE770583DE9B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Budget taken from web link, please check if this is correct</t>
+      </text>
+    </comment>
+    <comment ref="D27" authorId="9" shapeId="0" xr:uid="{2B238BD5-0FE1-4ABD-837C-4C765A136BD6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Budget taken from web link, please check if this is correct</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="143">
   <si>
     <t>Project ID</t>
   </si>
@@ -48,6 +259,9 @@
     <t>Budget</t>
   </si>
   <si>
+    <t>Output budget</t>
+  </si>
+  <si>
     <t>Beneficiary Category</t>
   </si>
   <si>
@@ -109,7 +323,10 @@
   </si>
   <si>
     <t xml:space="preserve"> By 2025, people in North Macedonia benefit from ambitious climate action, sustainably managed natural resources and
-well-preserved biodiversity through good environmental governance and disaster resilient communities._x000D_</t>
+well-preserved biodiversity through good environmental governance and disaster resilient communities.</t>
+  </si>
+  <si>
+    <t>Mptf-Joint Sdg Fund</t>
   </si>
   <si>
     <t>Non-VF</t>
@@ -145,109 +362,159 @@
     <t>81,000 MWh tonnes</t>
   </si>
   <si>
+    <t>Estimated GHG emissions avoided (tCO2e/year):  75654</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
+  </si>
+  <si>
+    <t>Renewable capacity added</t>
+  </si>
+  <si>
+    <t>Medium Enterprises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex disaggregated) of sub-loans (RE/EE) extended by PFIs </t>
+  </si>
+  <si>
+    <t>Total value of sub-loans extended</t>
+  </si>
+  <si>
+    <t>Business Model</t>
+  </si>
+  <si>
+    <t>Total value of performance- based payments allocated:</t>
+  </si>
+  <si>
+    <t>Capacity Building Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
+  </si>
+  <si>
+    <t>Number of loan officers trained on gender-disaggregated data collection and analysis</t>
+  </si>
+  <si>
+    <t>Campaign Participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of individuals reached through marketing efforts  </t>
+  </si>
+  <si>
+    <t>Expected annual energy saved  (MJ)</t>
+  </si>
+  <si>
+    <t>5,200 MWh -&gt; convert to MJ 18720000</t>
+  </si>
+  <si>
+    <t>Estimated GHG emissions avoided tCO2e/year= 4856.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total value of loans extended: </t>
+  </si>
+  <si>
+    <t>USD 6.5 M</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of loans extended by banks </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number (sex-disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
+  </si>
+  <si>
+    <t>Total value of performance-
+based payments allocated to returning migrants and
+remittance recipients:  $ 0.45 M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Number of loans extended to women and women-headed
+h ouse holds (in cluding returning migrant s and remit :  227</t>
+  </si>
+  <si>
+    <t>Number of loans extended to returning migrant s and
+remitt ance recipient s:  150  ( sex-
+di saaareaat ed)</t>
+  </si>
+  <si>
+    <t>Tackling Air Pollution in Skopje</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00110061</t>
+  </si>
+  <si>
+    <t>GHG Emission Reduction=2.23.  5.56t in 2019</t>
+  </si>
+  <si>
+    <t>Swedish Int'L Development Cooperation</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00129099</t>
+  </si>
+  <si>
+    <t>GHG emission Reduction : amount to be determined after selection of the measures</t>
+  </si>
+  <si>
+    <t>Scaling up action to tackle air pollution,</t>
+  </si>
+  <si>
+    <t> https://open.undp.org/projects/00129099</t>
+  </si>
+  <si>
+    <t>MW added</t>
+  </si>
+  <si>
+    <t>It is expected that around 24 kW of photovoltaic power plants will be installed (TBC)</t>
+  </si>
+  <si>
+    <t>Transportation and E-mobility Services</t>
+  </si>
+  <si>
+    <t>Street-cleaning vehicles, preferably electric, are expected to be procured, the exact MJ to be determined upon completion of the technical documentation.</t>
+  </si>
+  <si>
+    <t>To be determined upon completion of the technical documentation for the selected priority measures that will be implemented.</t>
+  </si>
+  <si>
+    <t>Development of five air quality plans is planned for the pilot municipalities of Kavadarci, Strumica, Kumanovo, Struga, and Gostivar, collectively supporting a population of approximately 245,131 citizens.</t>
+  </si>
+  <si>
+    <t>Output Title</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Energy Efficiency</t>
+  </si>
+  <si>
+    <t>USD 44.4 M</t>
+  </si>
+  <si>
+    <t>Scale up energy finance</t>
+  </si>
+  <si>
+    <t>Output 1: SMEs have greater access to finance for accelerating a transition to renewable energy and energy efficiency solutions. No. in Quantum: 00132098</t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
+  </si>
+  <si>
+    <t>Expected annual energy saved</t>
+  </si>
+  <si>
+    <t>Close the gap on energy access</t>
+  </si>
+  <si>
     <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <t>Estimated GHG emissions avoided (tCO2e/year)</t>
-  </si>
-  <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
-    <t>Renewable capacity added</t>
-  </si>
-  <si>
-    <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex disaggregated) of sub-loans (RE/EE) extended by PFIs </t>
-  </si>
-  <si>
-    <t>Total value of sub-loans extended</t>
-  </si>
-  <si>
-    <t>Business Model</t>
-  </si>
-  <si>
-    <t>Total value of performance- based payments allocated:</t>
-  </si>
-  <si>
-    <t>Capacity Building Training</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
-  </si>
-  <si>
-    <t>Number of loan officers trained on gender-disaggregated data collection and analysis</t>
-  </si>
-  <si>
-    <t>Campaign Participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of individuals reached through marketing efforts  </t>
-  </si>
-  <si>
-    <t>Expected annual energy saved  (MJ)</t>
-  </si>
-  <si>
-    <t>5,200 MWh -&gt; convert to MJ 18720000</t>
-  </si>
-  <si>
-    <t>Estimated GHG emissions avoided tCO2e/year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total value of loans extended: </t>
-  </si>
-  <si>
-    <t>USD 6.5 M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of loans extended by banks </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number (sex-disaggregated) of loan officers trained to assess RE/EE project loan applications </t>
-  </si>
-  <si>
-    <t>Tackling Air Pollution in Skopje</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00110061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculation of emissions </t>
-  </si>
-  <si>
-    <t>5.56t in 2019</t>
-  </si>
-  <si>
-    <t>Output Title</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Energy Efficiency</t>
-  </si>
-  <si>
-    <t>USD 44.4 M</t>
-  </si>
-  <si>
-    <t>Scale up energy finance</t>
-  </si>
-  <si>
-    <t>Output 1: SMEs have greater access to finance for accelerating a transition to renewable energy and energy efficiency solutions. No. in Quantum: 00132098</t>
-  </si>
-  <si>
-    <t>Other Energy Services</t>
-  </si>
-  <si>
-    <t>Expected annual energy saved</t>
-  </si>
-  <si>
-    <t>Close the gap on energy access</t>
   </si>
   <si>
     <t>$30.39 M</t>
@@ -269,6 +536,9 @@
     <t>5,200 MWh</t>
   </si>
   <si>
+    <t>Estimated GHG emissions avoided tCO2e/year</t>
+  </si>
+  <si>
     <t>USD 2.15 mil</t>
   </si>
   <si>
@@ -276,6 +546,12 @@
   </si>
   <si>
     <t>CO2 Emissions Reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculation of emissions </t>
+  </si>
+  <si>
+    <t>5.56t in 2019</t>
   </si>
   <si>
     <t xml:space="preserve">Estimated GHG emissions avoided </t>
@@ -357,9 +633,6 @@
     <t>Number of people who gain access to education services through clean energy systems (including students, teachers, etc.) </t>
   </si>
   <si>
-    <t>Transportation and E-mobility Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of MJ saved from transport and e-mobility interventions (e.g., electric vehicles, charging stations, etc.)  </t>
   </si>
   <si>
@@ -406,9 +679,6 @@
   </si>
   <si>
     <t xml:space="preserve">Number of people supported by policy and regulatory framework development on clean, affordable, and sustainable energy </t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>Any other type of beneficiary (please specify justification in Notes)</t>
@@ -418,7 +688,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,12 +761,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,8 +773,43 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -518,8 +822,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -678,6 +988,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -686,7 +1020,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -789,48 +1123,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -849,6 +1164,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -878,7 +1306,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -892,6 +1320,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Folashade Jaiyeola" id="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" userId="S::folashade.jaiyeola@undp.org::c208a32e-6303-48b2-9538-645490e99643" providerId="AD"/>
+  <person displayName="Gordana Popovikj Friedman" id="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" userId="S::gordana.popovikj.friedman@undp.org::99a5efa7-f829-4525-8197-01706efa92a6" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1179,32 +1614,120 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K2" dT="2024-11-22T19:10:13.16" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{79EEC1AE-897B-4A90-805B-F768C8A6C2CD}">
+    <text>I added the donor named based on the web link for this column, please check if this is correct</text>
+  </threadedComment>
+  <threadedComment ref="I3" dT="2024-11-22T18:41:27.42" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{621A9DFD-CCA8-4D76-B5B6-158D5A833901}">
+    <text>Note to system: The number relates to energy saved not number of beneficiaries</text>
+  </threadedComment>
+  <threadedComment ref="I3" dT="2024-11-25T12:29:04.95" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{0DB1A00D-B2FF-4EB4-ADA0-B269866981A3}" parentId="{621A9DFD-CCA8-4D76-B5B6-158D5A833901}">
+    <text>Correct.</text>
+  </threadedComment>
+  <threadedComment ref="J4" dT="2024-11-22T18:40:15.67" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{A08E9D70-5A23-46E7-B9E5-91D2EF7C552F}">
+    <text>I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</text>
+  </threadedComment>
+  <threadedComment ref="I6" dT="2024-11-25T12:32:39.76" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{D2FE1F41-7211-4981-AD33-0A9F681DCFBD}">
+    <text>Tentative/target number of SME beneficiaries of support (tech assistance, "green" loans and performance-based incentives) for RE/EE investments.</text>
+  </threadedComment>
+  <threadedComment ref="I16" dT="2024-11-22T18:37:27.83" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{891F3133-B0A9-4747-959A-2C56653BE395}">
+    <text>This should indicate the number of beneficiaries supported by this intervention</text>
+  </threadedComment>
+  <threadedComment ref="I16" dT="2024-11-25T12:30:21.34" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{67E0B355-A6CF-4722-9D8E-0A3FB24178C5}" parentId="{891F3133-B0A9-4747-959A-2C56653BE395}">
+    <text>It indicates an expected/target number of households/individuals supported (with tech assistance, "green" loans, and ex-post, performance-based incentives) for RE/EE investments.</text>
+  </threadedComment>
+  <threadedComment ref="I20" dT="2024-11-22T18:36:16.12" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{BC0B41C5-54B6-4044-85AB-618F19862654}">
+    <text>This should indicate the volume of investment (US dollars). Thank you for checking if this is correct.</text>
+  </threadedComment>
+  <threadedComment ref="I20" dT="2024-11-25T12:31:24.48" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{0AF225B4-3328-4483-9BE2-C183E4DE5000}" parentId="{BC0B41C5-54B6-4044-85AB-618F19862654}">
+    <text>This indicates the volume of *ex-post, performance-based incentives* attached to the investments (upon verification). The incentives for these groups of beneficiaries, though are payable by IOM (implementing partner in the project/GFF).</text>
+  </threadedComment>
+  <threadedComment ref="J23" dT="2024-11-22T18:51:17.04" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{23B597A5-1B66-4CAB-AA0F-F278334B7E92}">
+    <text>I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</text>
+  </threadedComment>
+  <threadedComment ref="D26" dT="2024-11-22T18:47:01.19" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{66639FD2-4E2E-4171-92B2-2E309852434A}">
+    <text>Budget taken from web link, please check if this is correct</text>
+  </threadedComment>
+  <threadedComment ref="D27" dT="2024-11-22T18:47:01.19" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{2EBE4A3C-45A5-419E-9453-DCAF8C235A44}">
+    <text>Budget taken from web link, please check if this is correct</text>
+  </threadedComment>
+  <threadedComment ref="D28" dT="2024-11-22T18:47:01.19" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{C03134EB-0D27-4781-BC31-6E10FCBCA97A}">
+    <text>Budget taken from web link, please check if this is correct</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="K2" dT="2024-11-22T19:10:13.16" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{9234F38C-6247-4C32-9C39-0813DCF2450F}">
+    <text>I added the donor named based on the web link for this column, please check if this is correct</text>
+  </threadedComment>
+  <threadedComment ref="I3" dT="2024-11-22T18:41:27.42" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{7A94FBEE-AD1F-467F-AD57-574F1E79D6C3}">
+    <text>Note to system: The number relates to energy saved not number of beneficiaries</text>
+  </threadedComment>
+  <threadedComment ref="I3" dT="2024-11-25T12:29:04.95" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{F915C7A0-1C17-4FE5-8D5C-D51D0F7A8467}" parentId="{7A94FBEE-AD1F-467F-AD57-574F1E79D6C3}">
+    <text>Correct.</text>
+  </threadedComment>
+  <threadedComment ref="J4" dT="2024-11-22T18:40:15.67" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{CA08CDE2-D4D6-4671-B38F-80F1DB89074F}">
+    <text>I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</text>
+  </threadedComment>
+  <threadedComment ref="I6" dT="2024-11-25T12:32:39.76" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{BDC16EA3-A8E2-496C-BBA7-C59FBD41AC51}">
+    <text>Tentative/target number of SME beneficiaries of support (tech assistance, "green" loans and performance-based incentives) for RE/EE investments.</text>
+  </threadedComment>
+  <threadedComment ref="I16" dT="2024-11-22T18:37:27.83" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{952459A9-C6C8-4831-8252-7617B7339F3E}">
+    <text>This should indicate the number of beneficiaries supported by this intervention</text>
+  </threadedComment>
+  <threadedComment ref="I16" dT="2024-11-25T12:30:21.34" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{91631459-648D-4D48-84D7-35C1749F002B}" parentId="{952459A9-C6C8-4831-8252-7617B7339F3E}">
+    <text>It indicates an expected/target number of households/individuals supported (with tech assistance, "green" loans, and ex-post, performance-based incentives) for RE/EE investments.</text>
+  </threadedComment>
+  <threadedComment ref="I20" dT="2024-11-22T18:36:16.12" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{C38306C6-5115-4A98-B84A-C3BE8B9B0A8B}">
+    <text>This should indicate the volume of investment (US dollars). Thank you for checking if this is correct.</text>
+  </threadedComment>
+  <threadedComment ref="I20" dT="2024-11-25T12:31:24.48" personId="{2C744443-592E-4DFA-B2F7-DD2AAA854B05}" id="{03036B92-1F2F-48A0-8DE0-A865D0F7CBB6}" parentId="{C38306C6-5115-4A98-B84A-C3BE8B9B0A8B}">
+    <text>This indicates the volume of *ex-post, performance-based incentives* attached to the investments (upon verification). The incentives for these groups of beneficiaries, though are payable by IOM (implementing partner in the project/GFF).</text>
+  </threadedComment>
+  <threadedComment ref="J23" dT="2024-11-22T18:51:17.04" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{10739C89-E707-417F-AB4E-5ABD4B510B80}">
+    <text>I moved the GHG emission date in the Note as our system doesn't support this kind of date in the Target column.</text>
+  </threadedComment>
+  <threadedComment ref="D25" dT="2024-11-22T18:47:01.19" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{8F310A7D-2DE2-4A4C-A359-FA3AEC7579AD}">
+    <text>Budget taken from web link, please check if this is correct</text>
+  </threadedComment>
+  <threadedComment ref="D26" dT="2024-11-22T18:47:01.19" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{8E2C567E-C0F8-4DD4-B60D-DE770583DE9B}">
+    <text>Budget taken from web link, please check if this is correct</text>
+  </threadedComment>
+  <threadedComment ref="D27" dT="2024-11-22T18:47:01.19" personId="{677AD49F-3492-411D-9D2E-6FC8BC25D7F7}" id="{2B238BD5-0FE1-4ABD-837C-4C765A136BD6}">
+    <text>Budget taken from web link, please check if this is correct</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1B1400-35FF-426D-9AE6-BEF15E5709CF}">
-  <dimension ref="A1:V23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92672B0A-9916-452E-AD42-D1214710D1E2}">
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" customWidth="1"/>
-    <col min="9" max="9" width="32.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" style="62" customWidth="1"/>
+    <col min="10" max="10" width="32.7109375" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1740,7 @@
       <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="96" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="35" t="s">
@@ -1229,845 +1752,1149 @@
       <c r="H1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="35" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="56" t="s">
+      <c r="N1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="56" t="s">
+      <c r="O1" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="P1" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="57" t="s">
+      <c r="Q1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="58" t="s">
+      <c r="R1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="59" t="s">
+      <c r="S1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="58" t="s">
+      <c r="T1" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="58" t="s">
+      <c r="U1" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="59" t="s">
+      <c r="V1" s="51" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" ht="106.5">
+      <c r="W1" s="52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="91.5">
       <c r="A2" s="33">
         <v>144953</v>
       </c>
-      <c r="B2" s="50" t="s">
-        <v>22</v>
+      <c r="B2" s="45" t="s">
+        <v>23</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="37">
         <v>95000</v>
       </c>
-      <c r="E2" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="33"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>25</v>
+      </c>
       <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
+      <c r="I2" s="58"/>
       <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="61" t="s">
+      <c r="K2" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="L2" s="33"/>
+      <c r="M2" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39" t="s">
+      <c r="N2" s="39"/>
+      <c r="O2" s="54" t="s">
         <v>28</v>
       </c>
+      <c r="P2" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="39"/>
       <c r="R2" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="S2" s="37"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="V2" s="37"/>
-    </row>
-    <row r="3" spans="1:22" ht="64.5" customHeight="1">
+      <c r="S2" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="37"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="37"/>
+    </row>
+    <row r="3" spans="1:23" ht="64.5" customHeight="1">
       <c r="A3" s="33">
         <v>144270</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="37">
+        <v>34</v>
+      </c>
+      <c r="D3" s="77">
         <v>44400000</v>
       </c>
-      <c r="E3" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="39">
-        <v>0</v>
-      </c>
-      <c r="H3" s="40">
+      <c r="E3" s="77"/>
+      <c r="F3" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="39">
+        <v>0</v>
+      </c>
+      <c r="I3" s="65">
         <v>291600000</v>
       </c>
-      <c r="I3" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="39"/>
-      <c r="N3" s="61" t="s">
+      <c r="J3" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="39"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="39"/>
+      <c r="O3" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P3" s="39"/>
       <c r="Q3" s="39"/>
       <c r="R3" s="39"/>
-      <c r="S3" s="37"/>
-      <c r="T3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="37"/>
       <c r="U3" s="39"/>
-      <c r="V3" s="37"/>
-    </row>
-    <row r="4" spans="1:22" ht="15" customHeight="1">
+      <c r="V3" s="39"/>
+      <c r="W3" s="37"/>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1">
       <c r="A4" s="37"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="39">
-        <v>0</v>
-      </c>
-      <c r="H4" s="43">
-        <v>75654</v>
-      </c>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="39"/>
-      <c r="N4" s="61" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39">
+        <v>0</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="39"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="39"/>
+      <c r="O4" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P4" s="39"/>
       <c r="Q4" s="39"/>
       <c r="R4" s="39"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="37"/>
       <c r="U4" s="39"/>
-      <c r="V4" s="37"/>
-    </row>
-    <row r="5" spans="1:22" ht="15" customHeight="1">
+      <c r="V4" s="39"/>
+      <c r="W4" s="37"/>
+    </row>
+    <row r="5" spans="1:23" ht="23.25" customHeight="1">
       <c r="A5" s="37"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="44" t="s">
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="39">
-        <v>0</v>
-      </c>
-      <c r="H5" s="45">
+      <c r="G5" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="39">
+        <v>0</v>
+      </c>
+      <c r="I5" s="88">
         <v>8.1</v>
       </c>
-      <c r="I5" s="33"/>
       <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="39"/>
-      <c r="N5" s="61" t="s">
+      <c r="K5" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="39"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="39"/>
+      <c r="O5" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P5" s="39"/>
       <c r="Q5" s="39"/>
       <c r="R5" s="39"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="37"/>
       <c r="U5" s="39"/>
-      <c r="V5" s="37"/>
-    </row>
-    <row r="6" spans="1:22" ht="40.5" customHeight="1">
+      <c r="V5" s="39"/>
+      <c r="W5" s="37"/>
+    </row>
+    <row r="6" spans="1:23" ht="40.5" customHeight="1">
       <c r="A6" s="37"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="44" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="39">
-        <v>0</v>
-      </c>
-      <c r="H6" s="45">
+      <c r="G6" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+      <c r="I6" s="89">
         <v>105</v>
       </c>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="39"/>
-      <c r="N6" s="61" t="s">
+      <c r="J6" s="55"/>
+      <c r="K6" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O6" s="39"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="39"/>
+      <c r="O6" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P6" s="39"/>
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="37"/>
       <c r="U6" s="39"/>
-      <c r="V6" s="37"/>
-    </row>
-    <row r="7" spans="1:22" ht="24.75" customHeight="1">
+      <c r="V6" s="39"/>
+      <c r="W6" s="37"/>
+    </row>
+    <row r="7" spans="1:23" ht="24.75" customHeight="1">
       <c r="A7" s="37"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="39">
-        <v>0</v>
-      </c>
-      <c r="H7" s="41">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0</v>
+      </c>
+      <c r="I7" s="90">
         <v>30390000</v>
       </c>
       <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="39"/>
-      <c r="N7" s="61" t="s">
+      <c r="K7" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O7" s="39"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="39"/>
+      <c r="O7" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="U7" s="39"/>
-      <c r="V7" s="37"/>
-    </row>
-    <row r="8" spans="1:22" ht="27.75" customHeight="1">
+      <c r="S7" s="39"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="V7" s="39"/>
+      <c r="W7" s="37"/>
+    </row>
+    <row r="8" spans="1:23" ht="27.75" customHeight="1">
       <c r="A8" s="37"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="39">
-        <v>0</v>
-      </c>
-      <c r="H8" s="41">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0</v>
+      </c>
+      <c r="I8" s="90">
         <v>3039000</v>
       </c>
       <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="39"/>
-      <c r="N8" s="61" t="s">
+      <c r="K8" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="39"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="39"/>
+      <c r="O8" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P8" s="39"/>
       <c r="Q8" s="39"/>
       <c r="R8" s="39"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="U8" s="39"/>
-      <c r="V8" s="37"/>
-    </row>
-    <row r="9" spans="1:22" ht="55.5" customHeight="1">
+      <c r="S8" s="39"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="V8" s="39"/>
+      <c r="W8" s="37"/>
+    </row>
+    <row r="9" spans="1:23" ht="55.5" customHeight="1">
       <c r="A9" s="37"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="38" t="s">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="39">
-        <v>0</v>
-      </c>
-      <c r="H9" s="46">
+      <c r="G9" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0</v>
+      </c>
+      <c r="I9" s="91">
         <v>20</v>
       </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="39"/>
-      <c r="N9" s="61" t="s">
+      <c r="J9" s="56"/>
+      <c r="K9" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O9" s="39"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="39"/>
+      <c r="O9" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P9" s="39"/>
       <c r="Q9" s="39"/>
       <c r="R9" s="39"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="39"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="37"/>
       <c r="U9" s="39"/>
-      <c r="V9" s="37"/>
-    </row>
-    <row r="10" spans="1:22" ht="41.25" customHeight="1">
+      <c r="V9" s="39"/>
+      <c r="W9" s="37"/>
+    </row>
+    <row r="10" spans="1:23" ht="41.25" customHeight="1">
       <c r="A10" s="37"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="39">
-        <v>0</v>
-      </c>
-      <c r="H10" s="46">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0</v>
+      </c>
+      <c r="I10" s="91">
         <v>20</v>
       </c>
-      <c r="I10" s="33"/>
       <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="39"/>
-      <c r="N10" s="61" t="s">
+      <c r="K10" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="39"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="39"/>
+      <c r="O10" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P10" s="39"/>
       <c r="Q10" s="39"/>
       <c r="R10" s="39"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="37"/>
       <c r="U10" s="39"/>
-      <c r="V10" s="37"/>
-    </row>
-    <row r="11" spans="1:22" ht="39.75" customHeight="1">
+      <c r="V10" s="39"/>
+      <c r="W10" s="37"/>
+    </row>
+    <row r="11" spans="1:23" ht="39.75" customHeight="1">
       <c r="A11" s="37"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="38" t="s">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="39">
-        <v>0</v>
-      </c>
-      <c r="H11" s="46">
+      <c r="G11" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0</v>
+      </c>
+      <c r="I11" s="91">
         <v>7000</v>
       </c>
-      <c r="I11" s="33"/>
       <c r="J11" s="33"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="39"/>
-      <c r="N11" s="61" t="s">
+      <c r="K11" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="39"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="39"/>
+      <c r="O11" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P11" s="39"/>
       <c r="Q11" s="39"/>
       <c r="R11" s="39"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="37"/>
       <c r="U11" s="39"/>
-      <c r="V11" s="37"/>
-    </row>
-    <row r="12" spans="1:22" ht="27.75" customHeight="1">
+      <c r="V11" s="39"/>
+      <c r="W11" s="37"/>
+    </row>
+    <row r="12" spans="1:23" ht="27.75" customHeight="1">
       <c r="A12" s="37"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="39">
-        <v>0</v>
-      </c>
-      <c r="H12" s="46">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="39">
+        <v>0</v>
+      </c>
+      <c r="I12" s="91">
         <v>18720000</v>
       </c>
-      <c r="I12" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="39"/>
-      <c r="N12" s="61" t="s">
+      <c r="J12" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O12" s="39"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="39"/>
+      <c r="O12" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P12" s="39"/>
       <c r="Q12" s="39"/>
       <c r="R12" s="39"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="37"/>
       <c r="U12" s="39"/>
-      <c r="V12" s="37"/>
-    </row>
-    <row r="13" spans="1:22" ht="24.75" customHeight="1">
+      <c r="V12" s="39"/>
+      <c r="W12" s="37"/>
+    </row>
+    <row r="13" spans="1:23" ht="24.75" customHeight="1">
       <c r="A13" s="37"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="39">
-        <v>0</v>
-      </c>
-      <c r="H13" s="48">
-        <v>4856.8</v>
-      </c>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="39"/>
-      <c r="N13" s="61" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="39"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="39"/>
+      <c r="O13" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P13" s="39"/>
       <c r="Q13" s="39"/>
       <c r="R13" s="39"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="37"/>
       <c r="U13" s="39"/>
-      <c r="V13" s="37"/>
-    </row>
-    <row r="14" spans="1:22" ht="20.25" customHeight="1">
+      <c r="V13" s="39"/>
+      <c r="W13" s="37"/>
+    </row>
+    <row r="14" spans="1:23" ht="20.25" customHeight="1">
       <c r="A14" s="37"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="49" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="39">
-        <v>0</v>
-      </c>
-      <c r="H14" s="46">
+      <c r="G14" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="39">
+        <v>0</v>
+      </c>
+      <c r="I14" s="92">
         <v>2.6</v>
       </c>
-      <c r="I14" s="33"/>
       <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="61" t="s">
+      <c r="K14" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O14" s="39"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="39"/>
+      <c r="O14" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P14" s="39"/>
       <c r="Q14" s="39"/>
       <c r="R14" s="39"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="37"/>
       <c r="U14" s="39"/>
-      <c r="V14" s="37"/>
-    </row>
-    <row r="15" spans="1:22" ht="20.25" customHeight="1">
+      <c r="V14" s="39"/>
+      <c r="W14" s="37"/>
+    </row>
+    <row r="15" spans="1:23" ht="20.25" customHeight="1">
       <c r="A15" s="37"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="39">
-        <v>0</v>
-      </c>
-      <c r="H15" s="46">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="39">
+        <v>0</v>
+      </c>
+      <c r="I15" s="78">
         <v>6500000</v>
       </c>
-      <c r="I15" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="61" t="s">
+      <c r="J15" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O15" s="39"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="39"/>
+      <c r="O15" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P15" s="39"/>
       <c r="Q15" s="39"/>
       <c r="R15" s="39"/>
-      <c r="S15" s="37"/>
-      <c r="T15" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="U15" s="39"/>
-      <c r="V15" s="37"/>
-    </row>
-    <row r="16" spans="1:22" ht="45.75">
+      <c r="S15" s="39"/>
+      <c r="T15" s="37"/>
+      <c r="U15" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" s="39"/>
+      <c r="W15" s="37"/>
+    </row>
+    <row r="16" spans="1:23" ht="45.75">
       <c r="A16" s="37"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="37" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="39">
-        <v>0</v>
-      </c>
-      <c r="H16" s="46">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="39">
+        <v>0</v>
+      </c>
+      <c r="I16" s="94">
         <v>650</v>
       </c>
-      <c r="I16" s="33"/>
       <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="61" t="s">
+      <c r="K16" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O16" s="39"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="39"/>
+      <c r="O16" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P16" s="39"/>
       <c r="Q16" s="39"/>
       <c r="R16" s="39"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="37"/>
       <c r="U16" s="39"/>
-      <c r="V16" s="37"/>
-    </row>
-    <row r="17" spans="1:22" ht="45.75">
+      <c r="V16" s="39"/>
+      <c r="W16" s="37"/>
+    </row>
+    <row r="17" spans="1:23" ht="45.75">
       <c r="A17" s="37"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="39">
-        <v>0</v>
-      </c>
-      <c r="H17" s="46">
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="39">
+        <v>0</v>
+      </c>
+      <c r="I17" s="91">
         <v>20</v>
       </c>
-      <c r="I17" s="33"/>
       <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="61" t="s">
+      <c r="K17" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O17" s="39"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="39"/>
+      <c r="O17" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P17" s="39"/>
       <c r="Q17" s="39"/>
       <c r="R17" s="39"/>
-      <c r="S17" s="37"/>
-      <c r="T17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="37"/>
       <c r="U17" s="39"/>
-      <c r="V17" s="37"/>
-    </row>
-    <row r="18" spans="1:22" ht="45.75">
+      <c r="V17" s="39"/>
+      <c r="W17" s="37"/>
+    </row>
+    <row r="18" spans="1:23" ht="45.75">
       <c r="A18" s="37"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="39">
-        <v>0</v>
-      </c>
-      <c r="H18" s="46">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="39">
+        <v>0</v>
+      </c>
+      <c r="I18" s="91">
         <v>20</v>
       </c>
-      <c r="I18" s="33"/>
       <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="39"/>
-      <c r="N18" s="61" t="s">
+      <c r="K18" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O18" s="39"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="39"/>
+      <c r="O18" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P18" s="39"/>
       <c r="Q18" s="39"/>
       <c r="R18" s="39"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="37"/>
       <c r="U18" s="39"/>
-      <c r="V18" s="37"/>
-    </row>
-    <row r="19" spans="1:22" ht="45.75">
+      <c r="V18" s="39"/>
+      <c r="W18" s="37"/>
+    </row>
+    <row r="19" spans="1:23" ht="45.75">
       <c r="A19" s="37"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="37" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="49" t="s">
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="39">
-        <v>0</v>
-      </c>
-      <c r="H19" s="51">
+      <c r="G19" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="39">
+        <v>0</v>
+      </c>
+      <c r="I19" s="91">
         <v>1000</v>
       </c>
-      <c r="I19" s="33"/>
       <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="39"/>
-      <c r="N19" s="61" t="s">
+      <c r="K19" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O19" s="39"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="39"/>
+      <c r="O19" s="54" t="s">
+        <v>28</v>
+      </c>
       <c r="P19" s="39"/>
       <c r="Q19" s="39"/>
       <c r="R19" s="39"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="39"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="37"/>
       <c r="U19" s="39"/>
-      <c r="V19" s="37"/>
-    </row>
-    <row r="20" spans="1:22" ht="45.75">
-      <c r="A20" s="50">
-        <v>110061</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="50">
-        <v>2150000</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="52" t="s">
+      <c r="V19" s="39"/>
+      <c r="W19" s="37"/>
+    </row>
+    <row r="20" spans="1:23" ht="53.25">
+      <c r="A20" s="37"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50">
-        <v>2.23</v>
-      </c>
-      <c r="I20" s="53" t="s">
-        <v>60</v>
+      <c r="H20" s="39">
+        <v>0</v>
+      </c>
+      <c r="I20" s="63">
+        <v>195</v>
       </c>
       <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="61" t="s">
+      <c r="K20" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="O20" s="39"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="54"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="39"/>
       <c r="R20" s="39"/>
-      <c r="S20" s="37"/>
-      <c r="T20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="37"/>
       <c r="U20" s="39"/>
-      <c r="V20" s="37"/>
-    </row>
-    <row r="21" spans="1:22">
-      <c r="F21" s="6"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-    </row>
-    <row r="22" spans="1:22">
-      <c r="F22" s="6"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-    </row>
-    <row r="23" spans="1:22">
-      <c r="F23" s="6"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="37"/>
+    </row>
+    <row r="21" spans="1:23" ht="53.25">
+      <c r="A21" s="37"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="39">
+        <v>0</v>
+      </c>
+      <c r="I21" s="63">
+        <v>100</v>
+      </c>
+      <c r="J21" s="33"/>
+      <c r="K21" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="33"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="39"/>
+      <c r="V21" s="39"/>
+      <c r="W21" s="37"/>
+    </row>
+    <row r="22" spans="1:23" ht="53.25">
+      <c r="A22" s="69"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="67">
+        <v>0</v>
+      </c>
+      <c r="I22" s="82">
+        <v>65</v>
+      </c>
+      <c r="J22" s="55"/>
+      <c r="K22" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="55"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="69"/>
+    </row>
+    <row r="23" spans="1:23" s="33" customFormat="1" ht="45.75">
+      <c r="A23" s="45">
+        <v>110061</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="45">
+        <v>2150000</v>
+      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="39"/>
+      <c r="O23" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="39"/>
+      <c r="V23" s="39"/>
+      <c r="W23" s="37"/>
+    </row>
+    <row r="24" spans="1:23" s="33" customFormat="1" ht="49.5" customHeight="1">
+      <c r="A24" s="45">
+        <v>129099</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="45">
+        <v>2110000</v>
+      </c>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="60"/>
+      <c r="J24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="39"/>
+      <c r="S24" s="39"/>
+      <c r="T24" s="37"/>
+      <c r="U24" s="39"/>
+      <c r="V24" s="39"/>
+      <c r="W24" s="37"/>
+    </row>
+    <row r="25" spans="1:23" s="64" customFormat="1" ht="46.5" customHeight="1">
+      <c r="A25" s="71">
+        <v>129099</v>
+      </c>
+      <c r="B25" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="97">
+        <v>3134309</v>
+      </c>
+      <c r="E25" s="97"/>
+      <c r="F25" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="71">
+        <v>0</v>
+      </c>
+      <c r="I25" s="73">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J25" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="K25" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="86"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="77"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="77"/>
+    </row>
+    <row r="26" spans="1:23" s="33" customFormat="1" ht="47.25" customHeight="1">
+      <c r="A26" s="71"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="72"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="K26" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="64"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="76"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="77"/>
+    </row>
+    <row r="27" spans="1:23" ht="48.75" customHeight="1">
+      <c r="A27" s="71"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="72"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="64"/>
+      <c r="M27" s="86"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="75"/>
+      <c r="S27" s="75"/>
+      <c r="T27" s="77"/>
+      <c r="U27" s="75"/>
+      <c r="V27" s="75"/>
+      <c r="W27" s="77"/>
+    </row>
+    <row r="28" spans="1:23" ht="50.25" customHeight="1">
+      <c r="A28" s="71"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="72"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="84">
+        <v>245131</v>
+      </c>
+      <c r="J28" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="L28" s="64"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="75"/>
+      <c r="R28" s="75"/>
+      <c r="S28" s="75"/>
+      <c r="T28" s="77"/>
+      <c r="U28" s="75"/>
+      <c r="V28" s="75"/>
+      <c r="W28" s="77"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="I29" s="61"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S21:S22" xr:uid="{1E190A99-9BFF-4CE9-AC67-306E550850B7}">
-      <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U28" xr:uid="{C925DFE2-C2DA-4702-9F91-4718B91C356B}">
+      <formula1>"Incentives and Support, Derisking Financial Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q20 R21:R22" xr:uid="{2001F045-7211-4118-BD15-E46516BB0DAB}">
-      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T28" xr:uid="{9515A593-D25A-4939-BA72-A253589B4A4F}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P20 Q21:Q22" xr:uid="{96AE7F23-217A-4AD9-B279-78255CC36D9A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S28" xr:uid="{A50485F9-05E8-4406-8299-3F7B854B16DF}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M28" xr:uid="{2A897502-9936-41AA-967E-E51863A6DA70}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V28" xr:uid="{78E5603E-B91B-488A-8A82-E7747438E8EC}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N28" xr:uid="{7C0844DD-BCF9-4072-9061-18CA10E417D1}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P28" xr:uid="{7BCD5010-23AF-4F45-A342-F8C227547A45}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O28" xr:uid="{77D8A213-7664-4DC5-9C9B-EE5917F1F3E3}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q28" xr:uid="{CD9257CF-30FE-42D7-A11D-D05F2EBED253}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O21:P22" xr:uid="{7679577C-5057-4CAE-A580-533A5173DCDC}">
-      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N22" xr:uid="{8BF837C9-DADF-4F73-B2BD-0382CD04DE67}">
-      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O20" xr:uid="{7AFDFACD-238C-4995-A371-0CB44E452D0E}">
-      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M20" xr:uid="{46DAB895-E9B1-4522-ABAF-25AE5B633D3B}">
-      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U20" xr:uid="{178070A3-1F94-4269-9451-493F2770BB30}">
-      <formula1>"National, Regional, City, Community"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L20" xr:uid="{4945BA84-8427-4530-86EA-3DBC336EB5D0}">
-      <formula1>"Non-VF, VF"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R20" xr:uid="{EAC35CAC-FDE6-4442-8588-CEC9F64480B7}">
-      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S20" xr:uid="{2832DC64-DEAC-4976-A1E2-F5A781EE6B22}">
-      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T20" xr:uid="{9FB228AE-3228-45AB-864A-0D934BACE7A9}">
-      <formula1>"Incentives and Support, Derisking Financial Model, Business Model"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R28" xr:uid="{25F7B321-6683-4ADA-ADCC-5075A490D1BC}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{E526A5E1-C5A6-4AA2-ABA5-1BC765442B72}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{A8C7CD7F-F779-4D37-8E5B-FC1B6B146550}"/>
-    <hyperlink ref="C20" r:id="rId3" xr:uid="{1057C5CB-3ACE-49CD-81D9-B6566CBF4DA9}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2C4541E0-3664-40CB-8AB7-8ABDAEEAB138}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{921BBF61-28B4-4F84-BBD2-C8EF2A721060}"/>
+    <hyperlink ref="C23" r:id="rId3" xr:uid="{902523E9-61C1-4DEC-AAA8-4130F63FC80D}"/>
+    <hyperlink ref="C25" r:id="rId4" xr:uid="{0BB26004-D8EB-4807-A438-F8D2282E89C2}"/>
+    <hyperlink ref="C24" r:id="rId5" xr:uid="{1E1034D7-BE24-49B3-9C61-1E780B3A2F89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId6"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66F8F0A6-363A-4C37-A85D-C0887B898825}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1B85B0CF-57A3-462D-8F46-9E9EC139B5C8}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E20</xm:sqref>
+          <xm:sqref>F2:F28</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2076,6 +2903,1171 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1B1400-35FF-426D-9AE6-BEF15E5709CF}">
+  <dimension ref="A1:W28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" style="62" customWidth="1"/>
+    <col min="10" max="10" width="32.7109375" customWidth="1"/>
+    <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="91.5">
+      <c r="A2" s="33">
+        <v>144953</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="37">
+        <v>95000</v>
+      </c>
+      <c r="E2" s="37"/>
+      <c r="F2" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="33"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="33"/>
+      <c r="M2" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="39"/>
+      <c r="O2" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="37"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" s="37"/>
+    </row>
+    <row r="3" spans="1:23" ht="64.5" customHeight="1">
+      <c r="A3" s="33">
+        <v>144270</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="77">
+        <v>44400000</v>
+      </c>
+      <c r="E3" s="77"/>
+      <c r="F3" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="39">
+        <v>0</v>
+      </c>
+      <c r="I3" s="65">
+        <v>291600000</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="33"/>
+      <c r="M3" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="39"/>
+      <c r="O3" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="37"/>
+    </row>
+    <row r="4" spans="1:23" ht="15" customHeight="1">
+      <c r="A4" s="37"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39">
+        <v>0</v>
+      </c>
+      <c r="I4" s="59"/>
+      <c r="J4" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="33"/>
+      <c r="M4" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="39"/>
+      <c r="O4" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="37"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="37"/>
+    </row>
+    <row r="5" spans="1:23" ht="23.25" customHeight="1">
+      <c r="A5" s="37"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="39">
+        <v>0</v>
+      </c>
+      <c r="I5" s="88">
+        <v>8.1</v>
+      </c>
+      <c r="J5" s="33"/>
+      <c r="K5" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="33"/>
+      <c r="M5" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="39"/>
+      <c r="O5" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="39"/>
+      <c r="R5" s="39"/>
+      <c r="S5" s="39"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="37"/>
+    </row>
+    <row r="6" spans="1:23" ht="40.5" customHeight="1">
+      <c r="A6" s="37"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="39">
+        <v>0</v>
+      </c>
+      <c r="I6" s="89">
+        <v>105</v>
+      </c>
+      <c r="J6" s="55"/>
+      <c r="K6" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="33"/>
+      <c r="M6" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="39"/>
+      <c r="O6" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="37"/>
+    </row>
+    <row r="7" spans="1:23" ht="24.75" customHeight="1">
+      <c r="A7" s="37"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="39">
+        <v>0</v>
+      </c>
+      <c r="I7" s="90">
+        <v>30390000</v>
+      </c>
+      <c r="J7" s="33"/>
+      <c r="K7" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="33"/>
+      <c r="M7" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="39"/>
+      <c r="O7" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="39"/>
+      <c r="R7" s="39"/>
+      <c r="S7" s="39"/>
+      <c r="T7" s="37"/>
+      <c r="U7" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="V7" s="39"/>
+      <c r="W7" s="37"/>
+    </row>
+    <row r="8" spans="1:23" ht="27.75" customHeight="1">
+      <c r="A8" s="37"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="39">
+        <v>0</v>
+      </c>
+      <c r="I8" s="90">
+        <v>3039000</v>
+      </c>
+      <c r="J8" s="33"/>
+      <c r="K8" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="33"/>
+      <c r="M8" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="39"/>
+      <c r="O8" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="V8" s="39"/>
+      <c r="W8" s="37"/>
+    </row>
+    <row r="9" spans="1:23" ht="55.5" customHeight="1">
+      <c r="A9" s="37"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="39">
+        <v>0</v>
+      </c>
+      <c r="I9" s="91">
+        <v>20</v>
+      </c>
+      <c r="J9" s="56"/>
+      <c r="K9" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="33"/>
+      <c r="M9" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="39"/>
+      <c r="O9" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="39"/>
+      <c r="R9" s="39"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="37"/>
+    </row>
+    <row r="10" spans="1:23" ht="41.25" customHeight="1">
+      <c r="A10" s="37"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="39">
+        <v>0</v>
+      </c>
+      <c r="I10" s="91">
+        <v>20</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" s="33"/>
+      <c r="M10" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="39"/>
+      <c r="O10" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="39"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="37"/>
+    </row>
+    <row r="11" spans="1:23" ht="39.75" customHeight="1">
+      <c r="A11" s="37"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="39">
+        <v>0</v>
+      </c>
+      <c r="I11" s="91">
+        <v>7000</v>
+      </c>
+      <c r="J11" s="33"/>
+      <c r="K11" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="43"/>
+      <c r="M11" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="39"/>
+      <c r="O11" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39"/>
+      <c r="S11" s="39"/>
+      <c r="T11" s="37"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="37"/>
+    </row>
+    <row r="12" spans="1:23" ht="27.75" customHeight="1">
+      <c r="A12" s="37"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="39">
+        <v>0</v>
+      </c>
+      <c r="I12" s="91">
+        <v>18720000</v>
+      </c>
+      <c r="J12" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="33"/>
+      <c r="M12" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="39"/>
+      <c r="O12" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39"/>
+      <c r="S12" s="39"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="37"/>
+    </row>
+    <row r="13" spans="1:23" ht="24.75" customHeight="1">
+      <c r="A13" s="37"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="33"/>
+      <c r="M13" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="39"/>
+      <c r="O13" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="37"/>
+    </row>
+    <row r="14" spans="1:23" ht="20.25" customHeight="1">
+      <c r="A14" s="37"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="39">
+        <v>0</v>
+      </c>
+      <c r="I14" s="92">
+        <v>2.6</v>
+      </c>
+      <c r="J14" s="33"/>
+      <c r="K14" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="33"/>
+      <c r="M14" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="39"/>
+      <c r="O14" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="37"/>
+    </row>
+    <row r="15" spans="1:23" ht="20.25" customHeight="1">
+      <c r="A15" s="37"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="39">
+        <v>0</v>
+      </c>
+      <c r="I15" s="78">
+        <v>6500000</v>
+      </c>
+      <c r="J15" s="93" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="33"/>
+      <c r="M15" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="39"/>
+      <c r="O15" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="37"/>
+      <c r="U15" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" s="39"/>
+      <c r="W15" s="37"/>
+    </row>
+    <row r="16" spans="1:23" ht="45.75">
+      <c r="A16" s="37"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="39">
+        <v>0</v>
+      </c>
+      <c r="I16" s="94">
+        <v>650</v>
+      </c>
+      <c r="J16" s="33"/>
+      <c r="K16" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="33"/>
+      <c r="M16" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="39"/>
+      <c r="O16" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39"/>
+      <c r="S16" s="39"/>
+      <c r="T16" s="37"/>
+      <c r="U16" s="39"/>
+      <c r="V16" s="39"/>
+      <c r="W16" s="37"/>
+    </row>
+    <row r="17" spans="1:23" ht="45.75">
+      <c r="A17" s="37"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="39">
+        <v>0</v>
+      </c>
+      <c r="I17" s="91">
+        <v>20</v>
+      </c>
+      <c r="J17" s="33"/>
+      <c r="K17" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="33"/>
+      <c r="M17" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="39"/>
+      <c r="O17" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39"/>
+      <c r="S17" s="39"/>
+      <c r="T17" s="37"/>
+      <c r="U17" s="39"/>
+      <c r="V17" s="39"/>
+      <c r="W17" s="37"/>
+    </row>
+    <row r="18" spans="1:23" ht="45.75">
+      <c r="A18" s="37"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="39">
+        <v>0</v>
+      </c>
+      <c r="I18" s="91">
+        <v>20</v>
+      </c>
+      <c r="J18" s="33"/>
+      <c r="K18" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="33"/>
+      <c r="M18" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="39"/>
+      <c r="O18" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="39"/>
+      <c r="T18" s="37"/>
+      <c r="U18" s="39"/>
+      <c r="V18" s="39"/>
+      <c r="W18" s="37"/>
+    </row>
+    <row r="19" spans="1:23" ht="45.75">
+      <c r="A19" s="37"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="39">
+        <v>0</v>
+      </c>
+      <c r="I19" s="91">
+        <v>1000</v>
+      </c>
+      <c r="J19" s="33"/>
+      <c r="K19" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="33"/>
+      <c r="M19" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="39"/>
+      <c r="O19" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="39"/>
+      <c r="S19" s="39"/>
+      <c r="T19" s="37"/>
+      <c r="U19" s="39"/>
+      <c r="V19" s="39"/>
+      <c r="W19" s="37"/>
+    </row>
+    <row r="20" spans="1:23" ht="53.25">
+      <c r="A20" s="37"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="39">
+        <v>0</v>
+      </c>
+      <c r="I20" s="63">
+        <v>195</v>
+      </c>
+      <c r="J20" s="33"/>
+      <c r="K20" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="33"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="39"/>
+      <c r="S20" s="39"/>
+      <c r="T20" s="37"/>
+      <c r="U20" s="39"/>
+      <c r="V20" s="39"/>
+      <c r="W20" s="37"/>
+    </row>
+    <row r="21" spans="1:23" ht="53.25">
+      <c r="A21" s="37"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="39">
+        <v>0</v>
+      </c>
+      <c r="I21" s="63">
+        <v>100</v>
+      </c>
+      <c r="J21" s="33"/>
+      <c r="K21" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="33"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="39"/>
+      <c r="V21" s="39"/>
+      <c r="W21" s="37"/>
+    </row>
+    <row r="22" spans="1:23" ht="53.25">
+      <c r="A22" s="69"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="67">
+        <v>0</v>
+      </c>
+      <c r="I22" s="82">
+        <v>65</v>
+      </c>
+      <c r="J22" s="55"/>
+      <c r="K22" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="55"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="67"/>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="69"/>
+    </row>
+    <row r="23" spans="1:23" s="33" customFormat="1" ht="45.75">
+      <c r="A23" s="45">
+        <v>110061</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="45">
+        <v>2150000</v>
+      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="K23" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="39"/>
+      <c r="O23" s="70" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39"/>
+      <c r="S23" s="39"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="39"/>
+      <c r="V23" s="39"/>
+      <c r="W23" s="37"/>
+    </row>
+    <row r="24" spans="1:23" s="64" customFormat="1" ht="46.5" customHeight="1">
+      <c r="A24" s="71">
+        <v>129099</v>
+      </c>
+      <c r="B24" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="97">
+        <v>3134309</v>
+      </c>
+      <c r="E24" s="97"/>
+      <c r="F24" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="71">
+        <v>0</v>
+      </c>
+      <c r="I24" s="73">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J24" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="K24" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="75"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="75"/>
+      <c r="T24" s="77"/>
+      <c r="U24" s="75"/>
+      <c r="V24" s="75"/>
+      <c r="W24" s="77"/>
+    </row>
+    <row r="25" spans="1:23" s="33" customFormat="1" ht="47.25" customHeight="1">
+      <c r="A25" s="71"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="72"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="K25" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="64"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="77"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="77"/>
+    </row>
+    <row r="26" spans="1:23" ht="48.75" customHeight="1">
+      <c r="A26" s="71"/>
+      <c r="B26" s="78"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="72"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="64"/>
+      <c r="M26" s="86"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="76"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="77"/>
+    </row>
+    <row r="27" spans="1:23" ht="50.25" customHeight="1">
+      <c r="A27" s="71"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="72"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="84">
+        <v>245131</v>
+      </c>
+      <c r="J27" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="64"/>
+      <c r="M27" s="86"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="76"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="75"/>
+      <c r="S27" s="75"/>
+      <c r="T27" s="77"/>
+      <c r="U27" s="75"/>
+      <c r="V27" s="75"/>
+      <c r="W27" s="77"/>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="I28" s="61"/>
+    </row>
+  </sheetData>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R27" xr:uid="{2001F045-7211-4118-BD15-E46516BB0DAB}">
+      <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q27" xr:uid="{96AE7F23-217A-4AD9-B279-78255CC36D9A}">
+      <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O27" xr:uid="{8BF837C9-DADF-4F73-B2BD-0382CD04DE67}">
+      <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P27" xr:uid="{7AFDFACD-238C-4995-A371-0CB44E452D0E}">
+      <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N27" xr:uid="{46DAB895-E9B1-4522-ABAF-25AE5B633D3B}">
+      <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V27" xr:uid="{178070A3-1F94-4269-9451-493F2770BB30}">
+      <formula1>"National, Regional, City, Community"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M27" xr:uid="{4945BA84-8427-4530-86EA-3DBC336EB5D0}">
+      <formula1>"Non-VF, VF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S27" xr:uid="{EAC35CAC-FDE6-4442-8588-CEC9F64480B7}">
+      <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T27" xr:uid="{2832DC64-DEAC-4976-A1E2-F5A781EE6B22}">
+      <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U27" xr:uid="{9FB228AE-3228-45AB-864A-0D934BACE7A9}">
+      <formula1>"Incentives and Support, Derisking Financial Model, Business Model"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{E526A5E1-C5A6-4AA2-ABA5-1BC765442B72}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{A8C7CD7F-F779-4D37-8E5B-FC1B6B146550}"/>
+    <hyperlink ref="C23" r:id="rId3" xr:uid="{1057C5CB-3ACE-49CD-81D9-B6566CBF4DA9}"/>
+    <hyperlink ref="C24" r:id="rId4" xr:uid="{72E96A84-96C3-4FB5-8418-75CC2EE9C21D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{66F8F0A6-363A-4C37-A85D-C0887B898825}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F27</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{097F89F9-6688-439D-801A-460CC8F3CB71}">
   <dimension ref="A1:T25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2099,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -2108,46 +4100,46 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -2155,10 +4147,10 @@
         <v>144953</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="6">
         <v>95000</v>
@@ -2170,10 +4162,10 @@
       <c r="J2" s="3"/>
       <c r="N2" s="31"/>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -2181,21 +4173,21 @@
         <v>144270</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F3" s="6"/>
       <c r="N3" s="31"/>
       <c r="P3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="Q3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S3" s="27"/>
       <c r="T3" s="27"/>
@@ -2203,30 +4195,30 @@
     <row r="4" spans="1:20" ht="39.75" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="32"/>
-      <c r="C4" s="63" t="s">
-        <v>67</v>
+      <c r="C4" s="99" t="s">
+        <v>82</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
       <c r="F4" s="6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H4" s="9">
         <v>0</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="29" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N4" s="31"/>
       <c r="P4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="Q4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S4" s="27"/>
       <c r="T4" s="27"/>
@@ -2234,14 +4226,14 @@
     <row r="5" spans="1:20" ht="15" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="32"/>
-      <c r="C5" s="63"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="32"/>
       <c r="E5" s="32"/>
       <c r="F5" s="6" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -2251,10 +4243,10 @@
       </c>
       <c r="N5" s="31"/>
       <c r="P5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S5" s="27"/>
       <c r="T5" s="27"/>
@@ -2262,14 +4254,14 @@
     <row r="6" spans="1:20" ht="15" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="32"/>
-      <c r="C6" s="63"/>
+      <c r="C6" s="99"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -2279,10 +4271,10 @@
       </c>
       <c r="N6" s="31"/>
       <c r="P6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S6" s="27"/>
       <c r="T6" s="27"/>
@@ -2290,14 +4282,14 @@
     <row r="7" spans="1:20" ht="40.5" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="63"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
       <c r="F7" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -2307,10 +4299,10 @@
       </c>
       <c r="N7" s="31"/>
       <c r="P7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S7" s="27"/>
       <c r="T7" s="27"/>
@@ -2318,28 +4310,28 @@
     <row r="8" spans="1:20" ht="24.75" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="32"/>
-      <c r="C8" s="63"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="29" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="N8" s="31"/>
       <c r="P8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S8" s="27"/>
       <c r="T8" s="27"/>
@@ -2347,28 +4339,28 @@
     <row r="9" spans="1:20" ht="27.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="32"/>
-      <c r="C9" s="63"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="29" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="N9" s="31"/>
       <c r="P9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S9" s="27"/>
       <c r="T9" s="27"/>
@@ -2376,14 +4368,14 @@
     <row r="10" spans="1:20" ht="55.5" customHeight="1">
       <c r="A10" s="6"/>
       <c r="B10" s="32"/>
-      <c r="C10" s="63"/>
+      <c r="C10" s="99"/>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
       <c r="F10" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -2393,10 +4385,10 @@
       </c>
       <c r="N10" s="31"/>
       <c r="P10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S10" s="27"/>
       <c r="T10" s="27"/>
@@ -2404,14 +4396,14 @@
     <row r="11" spans="1:20" ht="41.25" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="32"/>
-      <c r="C11" s="63"/>
+      <c r="C11" s="99"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
       <c r="F11" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -2421,10 +4413,10 @@
       </c>
       <c r="N11" s="31"/>
       <c r="P11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S11" s="27"/>
       <c r="T11" s="27"/>
@@ -2432,14 +4424,14 @@
     <row r="12" spans="1:20" ht="39.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="32"/>
-      <c r="C12" s="63"/>
+      <c r="C12" s="99"/>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
       <c r="F12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -2450,10 +4442,10 @@
       <c r="L12" s="5"/>
       <c r="N12" s="31"/>
       <c r="P12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q12" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S12" s="27"/>
       <c r="T12" s="27"/>
@@ -2461,28 +4453,28 @@
     <row r="13" spans="1:20" ht="27.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="32"/>
-      <c r="C13" s="63" t="s">
-        <v>74</v>
+      <c r="C13" s="99" t="s">
+        <v>91</v>
       </c>
       <c r="D13" s="32"/>
       <c r="E13" s="32"/>
       <c r="F13" s="6"/>
       <c r="G13" s="7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="29" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="N13" s="31"/>
       <c r="P13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S13" s="27"/>
       <c r="T13" s="27"/>
@@ -2490,14 +4482,14 @@
     <row r="14" spans="1:20" ht="24.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="32"/>
-      <c r="C14" s="63"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
       <c r="F14" s="6" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -2507,10 +4499,10 @@
       </c>
       <c r="N14" s="31"/>
       <c r="P14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S14" s="27"/>
       <c r="T14" s="27"/>
@@ -2518,14 +4510,14 @@
     <row r="15" spans="1:20" ht="20.25" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="32"/>
-      <c r="C15" s="63"/>
+      <c r="C15" s="99"/>
       <c r="D15" s="32"/>
       <c r="E15" s="32"/>
       <c r="F15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -2535,10 +4527,10 @@
       </c>
       <c r="N15" s="31"/>
       <c r="P15" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="Q15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S15" s="27"/>
       <c r="T15" s="27"/>
@@ -2546,26 +4538,26 @@
     <row r="16" spans="1:20" ht="20.25" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="32"/>
-      <c r="C16" s="63"/>
+      <c r="C16" s="99"/>
       <c r="D16" s="32"/>
       <c r="E16" s="32"/>
       <c r="F16" s="16"/>
       <c r="G16" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N16" s="31"/>
       <c r="P16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S16" s="27"/>
       <c r="T16" s="27"/>
@@ -2573,14 +4565,14 @@
     <row r="17" spans="1:20" ht="27">
       <c r="A17" s="6"/>
       <c r="B17" s="32"/>
-      <c r="C17" s="63"/>
+      <c r="C17" s="99"/>
       <c r="D17" s="32"/>
       <c r="E17" s="32"/>
       <c r="F17" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2590,10 +4582,10 @@
       </c>
       <c r="N17" s="31"/>
       <c r="P17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q17" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S17" s="27"/>
       <c r="T17" s="27"/>
@@ -2601,14 +4593,14 @@
     <row r="18" spans="1:20" ht="27">
       <c r="A18" s="6"/>
       <c r="B18" s="32"/>
-      <c r="C18" s="63"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="32"/>
       <c r="E18" s="32"/>
       <c r="F18" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2618,10 +4610,10 @@
       </c>
       <c r="N18" s="31"/>
       <c r="P18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q18" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S18" s="27"/>
       <c r="T18" s="27"/>
@@ -2629,14 +4621,14 @@
     <row r="19" spans="1:20" ht="27">
       <c r="A19" s="6"/>
       <c r="B19" s="32"/>
-      <c r="C19" s="63"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="32"/>
       <c r="E19" s="32"/>
       <c r="F19" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2646,10 +4638,10 @@
       </c>
       <c r="N19" s="31"/>
       <c r="P19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S19" s="27"/>
       <c r="T19" s="27"/>
@@ -2657,14 +4649,14 @@
     <row r="20" spans="1:20" ht="27">
       <c r="A20" s="6"/>
       <c r="B20" s="32"/>
-      <c r="C20" s="64"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="32"/>
       <c r="E20" s="32"/>
       <c r="F20" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2675,10 +4667,10 @@
       <c r="J20" s="15"/>
       <c r="N20" s="31"/>
       <c r="P20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S20" s="27"/>
       <c r="T20" s="27"/>
@@ -2688,14 +4680,14 @@
         <v>110061</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="20"/>
@@ -2704,10 +4696,10 @@
       <c r="J21" s="16"/>
       <c r="N21" s="31"/>
       <c r="P21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q21" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S21" s="27"/>
       <c r="T21" s="27"/>
@@ -2716,20 +4708,20 @@
       <c r="A22" s="22">
         <v>109164</v>
       </c>
-      <c r="B22" s="62" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
+      <c r="B22" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="98"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
       <c r="F22" s="23" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="I22" s="25">
         <v>3.33</v>
@@ -2737,10 +4729,10 @@
       <c r="J22" s="16"/>
       <c r="N22" s="31"/>
       <c r="P22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q22" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="S22" s="27"/>
       <c r="T22" s="27"/>
@@ -2809,7 +4801,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2838,22 +4830,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2861,10 +4853,10 @@
         <v>144953</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="6">
         <v>95000</v>
@@ -2880,86 +4872,86 @@
         <v>144270</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="39.75" customHeight="1">
-      <c r="A4" s="66">
+      <c r="A4" s="102">
         <v>144270</v>
       </c>
-      <c r="B4" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
+      <c r="B4" s="101" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
       <c r="E4" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="G4" s="9">
         <v>0</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30.75">
-      <c r="A5" s="66"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
+      <c r="A5" s="102"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
       <c r="E5" s="6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G5" s="9">
         <v>0</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="66"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
+      <c r="A6" s="102"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
       <c r="E6" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="9">
         <v>0</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="40.5" customHeight="1">
-      <c r="A7" s="66"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
+      <c r="A7" s="102"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="101"/>
       <c r="E7" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="9">
         <v>0</v>
@@ -2969,182 +4961,182 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A8" s="66"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
+      <c r="A8" s="102"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
       <c r="E8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A9" s="102"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="101"/>
+      <c r="D9" s="101"/>
+      <c r="E9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="55.5" customHeight="1">
+      <c r="A10" s="102"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A11" s="102"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="39.75" customHeight="1">
+      <c r="A12" s="102"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" s="5"/>
+    </row>
+    <row r="13" spans="1:11" ht="27.75" customHeight="1">
+      <c r="A13" s="102">
+        <v>144270</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="24.75" customHeight="1">
+      <c r="A14" s="102"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="20.25" customHeight="1">
+      <c r="A15" s="102"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="66"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="55.5" customHeight="1">
-      <c r="A10" s="66"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="41.25" customHeight="1">
-      <c r="A11" s="66"/>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="39.75" customHeight="1">
-      <c r="A12" s="66"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="66">
-        <v>144270</v>
-      </c>
-      <c r="B13" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A14" s="66"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A15" s="66"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="G15" s="9">
         <v>0</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1">
-      <c r="A16" s="66"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
+      <c r="A16" s="102"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
+      <c r="D16" s="101"/>
       <c r="E16" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" s="9">
         <v>0</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="27">
-      <c r="A17" s="66"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
+      <c r="A17" s="102"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" s="9">
         <v>0</v>
@@ -3154,51 +5146,51 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="27">
-      <c r="A18" s="66"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
+      <c r="A18" s="102"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="101"/>
+      <c r="D18" s="101"/>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G18" s="9">
         <v>0</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="27">
-      <c r="A19" s="66"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="101"/>
       <c r="E19" s="6" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="9">
         <v>0</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="27">
-      <c r="A20" s="66"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="101"/>
       <c r="E20" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G20" s="9">
         <v>0</v>
@@ -3213,13 +5205,13 @@
         <v>110061</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="20"/>
@@ -3231,22 +5223,22 @@
       <c r="A22" s="22">
         <v>109164</v>
       </c>
-      <c r="B22" s="67" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
+      <c r="B22" s="103" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
       <c r="E22" s="23" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H22" s="25" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I22" s="16"/>
     </row>
@@ -3288,7 +5280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3297,179 +5289,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="54" t="s">
+      <c r="A1" s="47" t="s">
         <v>5</v>
       </c>
+      <c r="B1" s="47" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>92</v>
+      <c r="A2" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="68" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="55" t="s">
-        <v>93</v>
+      <c r="A3" s="104" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="55" t="s">
-        <v>95</v>
+      <c r="A4" s="104" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="68" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="55" t="s">
-        <v>97</v>
+      <c r="A5" s="104" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="68" t="s">
-        <v>98</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>99</v>
+      <c r="A6" s="104" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="68" t="s">
-        <v>100</v>
-      </c>
-      <c r="B7" s="55" t="s">
-        <v>101</v>
+      <c r="A7" s="104" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="68" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="55" t="s">
-        <v>103</v>
+      <c r="A8" s="104" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>105</v>
+      <c r="A9" s="104" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="68" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="69" t="s">
-        <v>107</v>
+      <c r="A10" s="104" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="105" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>108</v>
+      <c r="A11" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="105" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="68" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="55" t="s">
-        <v>110</v>
+      <c r="A12" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="68" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>111</v>
+      <c r="A13" s="104" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="105" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="68" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="69" t="s">
-        <v>113</v>
+      <c r="A14" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="105" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="69" t="s">
-        <v>114</v>
+      <c r="A15" s="104" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="105" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="68" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="69" t="s">
-        <v>116</v>
+      <c r="A16" s="104" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="105" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="55" t="s">
-        <v>117</v>
+      <c r="A17" s="104" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" s="69" t="s">
-        <v>119</v>
+      <c r="A18" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="105" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="69" t="s">
-        <v>120</v>
+      <c r="A19" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="105" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="69" t="s">
-        <v>121</v>
+      <c r="A20" s="104" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="105" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="68" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="70" t="s">
-        <v>122</v>
+      <c r="A21" s="104" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="106" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="B22" s="69" t="s">
-        <v>124</v>
+      <c r="A22" s="104" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="105" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3478,15 +5470,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3741,6 +5724,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3753,11 +5745,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1F45FA-ADB1-42D5-8002-7349D9DEF3AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61DB48B0-5F5D-4664-9BF2-2988CF8E9CA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61DB48B0-5F5D-4664-9BF2-2988CF8E9CA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1F45FA-ADB1-42D5-8002-7349D9DEF3AA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/North Macedonia - Energy Projects.xlsx
@@ -4261,7 +4261,7 @@
       <c r="M28" s="123" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="R2:R27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -4291,12 +4291,6 @@
     </dataValidation>
     <dataValidation sqref="U2:U27" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Incentives and Support, Derisking Financial Model, Business Model"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
